--- a/delivery130/03_Excel_Deliveries/9_Growth_Projection.xlsx
+++ b/delivery130/03_Excel_Deliveries/9_Growth_Projection.xlsx
@@ -490,7 +490,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-28. Source: delivery130/04_Datasets — figures equal those cells.</t>
+          <t>Generated 2026-08-31. Source: delivery130/04_Datasets — figures equal those cells.</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
   </cols>
@@ -602,19 +602,19 @@
         </is>
       </c>
       <c r="C2" s="4" t="n">
-        <v>1872809.05</v>
+        <v>1872809.25</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>13378431.18</v>
+        <v>13378431.17</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>12392054.33</v>
+        <v>12392054.36</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>14421712.76</v>
+        <v>14421712.71</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>20067646769.56</v>
+        <v>20067646755</v>
       </c>
       <c r="H2" s="5" t="n">
         <v>92</v>
@@ -637,19 +637,19 @@
         </is>
       </c>
       <c r="C3" s="4" t="n">
-        <v>2323531.24</v>
+        <v>2323531.26</v>
       </c>
       <c r="D3" s="4" t="n">
         <v>15117928.25</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>14003300.22</v>
+        <v>14003300.25</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>16296859.91</v>
+        <v>16296859.86</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>22676892382.5</v>
+        <v>22676892375</v>
       </c>
       <c r="H3" s="5" t="n">
         <v>108</v>
@@ -672,19 +672,19 @@
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>3218095.29</v>
+        <v>3218095.33</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>14804020.88</v>
+        <v>14804020.86</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>13712536.89</v>
+        <v>13712536.91</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>15958473.3</v>
+        <v>15958473.24</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>22206031318.2</v>
+        <v>22206031290</v>
       </c>
       <c r="H4" s="5" t="n">
         <v>117</v>
@@ -707,19 +707,19 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>4262611.02</v>
+        <v>4262610.88</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>15157538.93</v>
+        <v>15157538.92</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>14039990.45</v>
+        <v>14039990.47</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>16339559.52</v>
+        <v>16339559.47</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>22736308394.13</v>
+        <v>22736308380</v>
       </c>
       <c r="H5" s="5" t="n">
         <v>118</v>
@@ -742,19 +742,19 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>3987687.48</v>
+        <v>3987687.47</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>14558691.37</v>
+        <v>14558691.36</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>13485295.25</v>
+        <v>13485295.28</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>15694012.42</v>
+        <v>15694012.37</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>21838037053.76</v>
+        <v>21838037040</v>
       </c>
       <c r="H6" s="5" t="n">
         <v>119</v>
@@ -777,19 +777,19 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>4568682.57</v>
+        <v>4568682.54</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>16451648.83</v>
+        <v>16451648.82</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>15238687.06</v>
+        <v>15238687.09</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>17734587.15</v>
+        <v>17734587.1</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>24677473238.38</v>
+        <v>24677473230</v>
       </c>
       <c r="H7" s="5" t="n">
         <v>119</v>
@@ -812,19 +812,19 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>5247262.94</v>
+        <v>5247262.97</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>16110048.19</v>
+        <v>16110048.17</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>14922272.26</v>
+        <v>14922272.28</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>17366347.69</v>
+        <v>17366347.64</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>24165072283.38</v>
+        <v>24165072255</v>
       </c>
       <c r="H8" s="5" t="n">
         <v>119</v>
@@ -847,19 +847,19 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>5432256.93</v>
+        <v>5432256.97</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>16494754</v>
+        <v>16494753.99</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>15278614.14</v>
+        <v>15278614.17</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>17781053.77</v>
+        <v>17781053.72</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>24742130997.14</v>
+        <v>24742130985</v>
       </c>
       <c r="H9" s="5" t="n">
         <v>120</v>
@@ -882,19 +882,19 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>5875940.5</v>
+        <v>5875940.51</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>15843075.44</v>
+        <v>15843075.43</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>14674983.11</v>
+        <v>14674983.14</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>17078555.78</v>
+        <v>17078555.73</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>23764613152.59</v>
+        <v>23764613145</v>
       </c>
       <c r="H10" s="5" t="n">
         <v>121</v>
@@ -917,19 +917,19 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>6943010.28</v>
+        <v>6943010.24</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>17903031.72</v>
+        <v>17903031.71</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>16583061.11</v>
+        <v>16583061.14</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>19299152.3</v>
+        <v>19299152.25</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>26854547579.06</v>
+        <v>26854547565</v>
       </c>
       <c r="H11" s="5" t="n">
         <v>121</v>
@@ -952,19 +952,19 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>8947657.73</v>
+        <v>8947657.74</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>17531294.69</v>
+        <v>17531294.68</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>16238731.84</v>
+        <v>16238731.86</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>18898426.35</v>
+        <v>18898426.29</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>26296942037.66</v>
+        <v>26296942020</v>
       </c>
       <c r="H12" s="5" t="n">
         <v>121</v>
@@ -987,19 +987,19 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>12461484.45</v>
+        <v>12461484.56</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>17949939.68</v>
+        <v>17949939.67</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>16626510.59</v>
+        <v>16626510.63</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>19349718.26</v>
+        <v>19349718.2</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>26924909517.75</v>
+        <v>26924909505</v>
       </c>
       <c r="H13" s="5" t="n">
         <v>122</v>
@@ -1022,19 +1022,19 @@
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>12522069.95</v>
+        <v>12522069.94</v>
       </c>
       <c r="D14" s="4" t="n">
         <v>17240769.3</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>15969626.56</v>
+        <v>15969626.6</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>18585245.1</v>
+        <v>18585245.06</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>25861153953.62</v>
+        <v>25861153950</v>
       </c>
       <c r="H14" s="5" t="n">
         <v>123</v>
@@ -1057,19 +1057,19 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>13725219.46</v>
+        <v>13725219.54</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>19482457.24</v>
+        <v>19482457.23</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>18046037.34</v>
+        <v>18046037.38</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>21001745.14</v>
+        <v>21001745.09</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>29223685857.53</v>
+        <v>29223685845</v>
       </c>
       <c r="H15" s="5" t="n">
         <v>123</v>
@@ -1092,19 +1092,19 @@
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>16545833.57</v>
+        <v>16545833.53</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>19077925.15</v>
+        <v>19077925.14</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>17671330.96</v>
+        <v>17671330.99</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>20565666.7</v>
+        <v>20565666.63</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>28616887730.46</v>
+        <v>28616887710</v>
       </c>
       <c r="H16" s="5" t="n">
         <v>126</v>
@@ -1127,19 +1127,19 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>17741891.82</v>
+        <v>17741891.81</v>
       </c>
       <c r="D17" s="4" t="n">
         <v>19533503.47</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>18093319.99</v>
+        <v>18093320.03</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>21056772.08</v>
+        <v>21056772.03</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>29300255205.29</v>
+        <v>29300255205</v>
       </c>
       <c r="H17" s="5" t="n">
         <v>128</v>
@@ -1162,19 +1162,19 @@
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>19660327.33</v>
+        <v>19660327.37</v>
       </c>
       <c r="D18" s="4" t="n">
         <v>18761769.29</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>17378484.91</v>
+        <v>17378484.95</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>20224856.25</v>
+        <v>20224856.2</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>28142653933.34</v>
+        <v>28142653935</v>
       </c>
       <c r="H18" s="5" t="n">
         <v>128</v>
@@ -1197,19 +1197,19 @@
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>23324978.68</v>
+        <v>23324978.72</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>21201221.45</v>
+        <v>21201221.44</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>19638078.97</v>
+        <v>19638079.02</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>22854542.63</v>
+        <v>22854542.58</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>31801832169.59</v>
+        <v>31801832160</v>
       </c>
       <c r="H19" s="5" t="n">
         <v>128</v>
@@ -1232,19 +1232,19 @@
         </is>
       </c>
       <c r="C20" s="4" t="n">
-        <v>20941938.88</v>
+        <v>20941938.91</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>20761001.09</v>
+        <v>20761001.08</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>19230315.57</v>
+        <v>19230315.61</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>22379992.86</v>
+        <v>22379992.79</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>31141501631.82</v>
+        <v>31141501620</v>
       </c>
       <c r="H20" s="5" t="n">
         <v>128</v>
@@ -1267,19 +1267,19 @@
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>21429816.81</v>
+        <v>21429816.82</v>
       </c>
       <c r="D21" s="4" t="n">
         <v>21256771.03</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>19689532.95</v>
+        <v>19689533</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>22914424.11</v>
+        <v>22914424.05</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>31885156551.01</v>
+        <v>31885156545</v>
       </c>
       <c r="H21" s="5" t="n">
         <v>128</v>
@@ -1302,19 +1302,19 @@
         </is>
       </c>
       <c r="C22" s="4" t="n">
-        <v>20850286.9</v>
+        <v>20850286.89</v>
       </c>
       <c r="D22" s="4" t="n">
         <v>20416953.6</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>18911634.32</v>
+        <v>18911634.37</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>22009115.73</v>
+        <v>22009115.68</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>30625430397.73</v>
+        <v>30625430400</v>
       </c>
       <c r="H22" s="5" t="n">
         <v>128</v>
@@ -1337,19 +1337,19 @@
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>23032148.29</v>
+        <v>23032148.22</v>
       </c>
       <c r="D23" s="4" t="n">
         <v>23071616.96</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>21370572.31</v>
+        <v>21370572.36</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>24870795.99</v>
+        <v>24870795.94</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>34607425438.16</v>
+        <v>34607425440</v>
       </c>
       <c r="H23" s="5" t="n">
         <v>128</v>
@@ -1372,19 +1372,19 @@
         </is>
       </c>
       <c r="C24" s="4" t="n">
-        <v>23051208.68</v>
+        <v>23051208.66</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>22592559.87</v>
+        <v>22592559.86</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>20926835.56</v>
+        <v>20926835.6</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>24354380.9</v>
+        <v>24354380.84</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>33888839800.43</v>
+        <v>33888839790</v>
       </c>
       <c r="H24" s="5" t="n">
         <v>128</v>
@@ -1407,19 +1407,19 @@
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>23152246.3</v>
+        <v>23152246.24</v>
       </c>
       <c r="D25" s="4" t="n">
         <v>23132067.19</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>21426565.61</v>
+        <v>21426565.67</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>24935960.28</v>
+        <v>24935960.22</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>34698100789.87</v>
+        <v>34698100785</v>
       </c>
       <c r="H25" s="5" t="n">
         <v>129</v>
@@ -1442,19 +1442,19 @@
         </is>
       </c>
       <c r="C26" s="4" t="n">
-        <v>20985647.53</v>
+        <v>20985647.56</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>22218160.12</v>
+        <v>22218160.13</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>20580039.89</v>
+        <v>20580039.95</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>23950784.58</v>
+        <v>23950784.53</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>33327240183.81</v>
+        <v>33327240195</v>
       </c>
       <c r="H26" s="5" t="n">
         <v>130</v>
@@ -1477,19 +1477,19 @@
         </is>
       </c>
       <c r="C27" s="4" t="n">
-        <v>24001481.39</v>
+        <v>24001481.5</v>
       </c>
       <c r="D27" s="4" t="n">
         <v>25107020.86</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>23255908.14</v>
+        <v>23255908.2</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>27064925.49</v>
+        <v>27064925.43</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>37660531288.61</v>
+        <v>37660531290</v>
       </c>
       <c r="H27" s="5" t="n">
         <v>130</v>
@@ -1512,19 +1512,19 @@
         </is>
       </c>
       <c r="C28" s="4" t="n">
-        <v>23834738.62</v>
+        <v>23834738.58</v>
       </c>
       <c r="D28" s="4" t="n">
         <v>24585700.81</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>22773024.44</v>
+        <v>22773024.49</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>26502951.68</v>
+        <v>26502951.6</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>36878551220.73</v>
+        <v>36878551215</v>
       </c>
       <c r="H28" s="5" t="n">
         <v>130</v>
@@ -1547,19 +1547,19 @@
         </is>
       </c>
       <c r="C29" s="4" t="n">
-        <v>24891805.65</v>
+        <v>24891805.71</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>25172804.08</v>
+        <v>25172804.09</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>23316841.24</v>
+        <v>23316841.3</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>27135838.64</v>
+        <v>27135838.58</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>37759206121.45</v>
+        <v>37759206135</v>
       </c>
       <c r="H29" s="5" t="n">
         <v>129</v>
@@ -1582,19 +1582,19 @@
         </is>
       </c>
       <c r="C30" s="4" t="n">
-        <v>25010048.04</v>
+        <v>25010048.03</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>24178271.1</v>
+        <v>24178271.11</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>22395634.07</v>
+        <v>22395634.13</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>26063749.64</v>
+        <v>26063749.58</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>36267406656.64</v>
+        <v>36267406665</v>
       </c>
       <c r="H30" s="5" t="n">
         <v>129</v>
@@ -1617,19 +1617,19 @@
         </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>28565229.2</v>
+        <v>28565229.17</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>27321990.37</v>
+        <v>27321990.38</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>25307570.42</v>
+        <v>25307570.48</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>29452623.54</v>
+        <v>29452623.48</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>40982985558.25</v>
+        <v>40982985570</v>
       </c>
       <c r="H31" s="5" t="n">
         <v>128</v>
@@ -1652,19 +1652,19 @@
         </is>
       </c>
       <c r="C32" s="4" t="n">
-        <v>28556269.78</v>
+        <v>28556269.83</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>26754678.89</v>
+        <v>26754678.88</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>24782086.18</v>
+        <v>24782086.23</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>28841071.77</v>
+        <v>28841071.7</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>40132018332.56</v>
+        <v>40132018320</v>
       </c>
       <c r="H32" s="5" t="n">
         <v>128</v>
@@ -1688,16 +1688,16 @@
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" s="4" t="n">
-        <v>27393577.06</v>
+        <v>27393577.07</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>25373879.1</v>
+        <v>25373879.17</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>29529792.73</v>
+        <v>29529792.67</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>41090365595.41</v>
+        <v>41090365605</v>
       </c>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
@@ -1719,16 +1719,16 @@
       </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" s="4" t="n">
-        <v>26311305.27</v>
+        <v>26311305.28</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>24371402.01</v>
+        <v>24371402.07</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>28363122.84</v>
+        <v>28363122.78</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>39466957910.23</v>
+        <v>39466957920</v>
       </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
@@ -1750,16 +1750,16 @@
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" s="4" t="n">
-        <v>29732366.98</v>
+        <v>29732366.99</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>27540232.64</v>
+        <v>27540232.71</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>32050966.99</v>
+        <v>32050966.93</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>44598550466.43</v>
+        <v>44598550485</v>
       </c>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
@@ -1784,13 +1784,13 @@
         <v>29115006.64</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>26968389.59</v>
+        <v>26968389.65</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>31385463.44</v>
+        <v>31385463.36</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>43672509958.56</v>
+        <v>43672509960</v>
       </c>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
@@ -1812,16 +1812,16 @@
       </c>
       <c r="C37" t="inlineStr"/>
       <c r="D37" s="4" t="n">
-        <v>29810269.13</v>
+        <v>29810269.14</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>27612391.15</v>
+        <v>27612391.23</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>32134944.13</v>
+        <v>32134944.07</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>44715403690.79</v>
+        <v>44715403710</v>
       </c>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
@@ -1843,16 +1843,16 @@
       </c>
       <c r="C38" t="inlineStr"/>
       <c r="D38" s="4" t="n">
-        <v>28632518.11</v>
+        <v>28632518.12</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>26521474.4</v>
+        <v>26521474.48</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>30865349.31</v>
+        <v>30865349.26</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>42948777160.56</v>
+        <v>42948777180</v>
       </c>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
@@ -1874,16 +1874,16 @@
       </c>
       <c r="C39" t="inlineStr"/>
       <c r="D39" s="4" t="n">
-        <v>32355389.71</v>
+        <v>32355389.72</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>29969862.82</v>
+        <v>29969862.91</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>34878539.21</v>
+        <v>34878539.14</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>48533084562.12</v>
+        <v>48533084580</v>
       </c>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
@@ -1908,13 +1908,13 @@
         <v>31683565.15</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>29347571.14</v>
+        <v>29347571.21</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>34154324.19</v>
+        <v>34154324.11</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>47525347723.01</v>
+        <v>47525347725</v>
       </c>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
@@ -1990,13 +1990,13 @@
         <v>2019</v>
       </c>
       <c r="B2" s="4" t="n">
-        <v>11677046.6</v>
+        <v>11677046.72</v>
       </c>
       <c r="C2" s="4" t="n">
-        <v>58457919.24</v>
+        <v>58457919.2</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>87686878860</v>
+        <v>87686878800</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -2015,13 +2015,13 @@
         <v>2020</v>
       </c>
       <c r="B3" s="4" t="n">
-        <v>19235889.92</v>
+        <v>19235889.95</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>63615142.39</v>
+        <v>63615142.34</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>95422713585</v>
+        <v>95422713510</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -2040,13 +2040,13 @@
         <v>2021</v>
       </c>
       <c r="B4" s="4" t="n">
-        <v>34228092.96</v>
+        <v>34228093.05</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>69227341.53</v>
+        <v>69227341.48999999</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>103841012295</v>
+        <v>103841012235</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -2065,13 +2065,13 @@
         <v>2022</v>
       </c>
       <c r="B5" s="4" t="n">
-        <v>60535014.8</v>
+        <v>60535014.82</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>75334655.16</v>
+        <v>75334655.14</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>113001982740</v>
+        <v>113001982710</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -2090,13 +2090,13 @@
         <v>2023</v>
       </c>
       <c r="B6" s="4" t="n">
-        <v>85357061.7</v>
+        <v>85357061.81999999</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>81980762.86</v>
+        <v>81980762.84</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>122971144290</v>
+        <v>122971144260</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -2115,13 +2115,13 @@
         <v>2024</v>
       </c>
       <c r="B7" s="4" t="n">
-        <v>90085890.17</v>
+        <v>90085890.01000001</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>89213197.62</v>
+        <v>89213197.61</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>133819796430</v>
+        <v>133819796415</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -2140,13 +2140,13 @@
         <v>2025</v>
       </c>
       <c r="B8" s="4" t="n">
-        <v>93713673.19</v>
+        <v>93713673.34999999</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>97083685.87</v>
+        <v>97083685.89</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>145625528805</v>
+        <v>145625528835</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -2165,13 +2165,13 @@
         <v>2026</v>
       </c>
       <c r="B9" s="4" t="n">
-        <v>82131547.02</v>
+        <v>82131547.03</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>105648517.42</v>
+        <v>105648517.44</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>158472776130</v>
+        <v>158472776160</v>
       </c>
       <c r="E9" t="n">
         <v>1</v>
@@ -2193,10 +2193,10 @@
         <v>0</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>114968948.02</v>
+        <v>114968948.05</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>172453422030</v>
+        <v>172453422075</v>
       </c>
       <c r="E10" t="n">
         <v>4</v>
@@ -2218,10 +2218,10 @@
         <v>0</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>92671472.97</v>
+        <v>92671472.98999999</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>139007209455</v>
+        <v>139007209485</v>
       </c>
       <c r="E11" t="n">
         <v>3</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="C2" s="4" t="n">
-        <v>186236.59</v>
+        <v>186236.61</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2560,7 +2560,7 @@
         <v>3036780.74</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>42960525.64</v>
+        <v>42960525.69</v>
       </c>
       <c r="G2" t="n">
         <v>31</v>
@@ -2586,7 +2586,7 @@
         </is>
       </c>
       <c r="C3" s="4" t="n">
-        <v>13047.64</v>
+        <v>13047.63</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2594,10 +2594,10 @@
         </is>
       </c>
       <c r="E3" s="4" t="n">
-        <v>2022343.05</v>
+        <v>2022343.04</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>37196147.88</v>
+        <v>37196147.9</v>
       </c>
       <c r="G3" t="n">
         <v>31</v>
@@ -2634,7 +2634,7 @@
         <v>2542924.08</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>25547585.57</v>
+        <v>25547585.53</v>
       </c>
       <c r="G4" t="n">
         <v>30</v>
@@ -2666,7 +2666,7 @@
         </is>
       </c>
       <c r="E5" s="4" t="n">
-        <v>1287564.18</v>
+        <v>1287564.19</v>
       </c>
       <c r="F5" s="4" t="n">
         <v>24381708.74</v>
@@ -2695,7 +2695,7 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>85.18000000000001</v>
+        <v>85.17</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
         <v>787978.34</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>22213149.53</v>
+        <v>22213149.57</v>
       </c>
       <c r="G6" t="n">
         <v>31</v>
@@ -2778,7 +2778,7 @@
         <v>988820.34</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>18832180.06</v>
+        <v>18832180.03</v>
       </c>
       <c r="G8" t="n">
         <v>30</v>
@@ -2813,7 +2813,7 @@
         <v>1079009.1</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>15352902.46</v>
+        <v>15352902.44</v>
       </c>
       <c r="G9" t="n">
         <v>28</v>
@@ -2837,7 +2837,7 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>5183.25</v>
+        <v>5183.26</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2845,10 +2845,10 @@
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>699292.22</v>
+        <v>699292.23</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>14554700.62</v>
+        <v>14554700.57</v>
       </c>
       <c r="G10" t="n">
         <v>31</v>
@@ -2874,7 +2874,7 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>13198.43</v>
+        <v>13198.41</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2885,7 +2885,7 @@
         <v>447818.47</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>10816064.97</v>
+        <v>10816064.96</v>
       </c>
       <c r="G11" t="n">
         <v>31</v>
@@ -2922,7 +2922,7 @@
         <v>947262.58</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>10729833.18</v>
+        <v>10729833.23</v>
       </c>
       <c r="G12" t="n">
         <v>29</v>
@@ -2957,7 +2957,7 @@
         <v>437255.96</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>10347004.49</v>
+        <v>10347004.44</v>
       </c>
       <c r="G13" t="n">
         <v>29</v>
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>197878.98</v>
+        <v>197878.99</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
         <v>280354.33</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>10114272.17</v>
+        <v>10114272.21</v>
       </c>
       <c r="G14" t="n">
         <v>31</v>
@@ -3018,7 +3018,7 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>2294.34</v>
+        <v>2294.33</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -3026,10 +3026,10 @@
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>367371.13</v>
+        <v>367371.14</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>8484168.210000001</v>
+        <v>8484168.189999999</v>
       </c>
       <c r="G15" t="n">
         <v>31</v>
@@ -3066,7 +3066,7 @@
         <v>460075.44</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>7410299.61</v>
+        <v>7410299.57</v>
       </c>
       <c r="G16" t="n">
         <v>29</v>
@@ -3098,10 +3098,10 @@
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>276574.69</v>
+        <v>276574.7</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>7216616.44</v>
+        <v>7216616.46</v>
       </c>
       <c r="G17" t="n">
         <v>31</v>
@@ -3127,7 +3127,7 @@
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>308.81</v>
+        <v>308.82</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3135,10 +3135,10 @@
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>331953.8</v>
+        <v>331953.81</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>6823995.85</v>
+        <v>6823995.89</v>
       </c>
       <c r="G18" t="n">
         <v>31</v>
@@ -3172,10 +3172,10 @@
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>510451.7</v>
+        <v>510451.71</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>6746466.29</v>
+        <v>6746466.3</v>
       </c>
       <c r="G19" t="n">
         <v>24</v>
@@ -3207,10 +3207,10 @@
         </is>
       </c>
       <c r="E20" s="4" t="n">
-        <v>367389.93</v>
+        <v>367389.92</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>6528915.83</v>
+        <v>6528915.81</v>
       </c>
       <c r="G20" t="n">
         <v>31</v>
@@ -3247,7 +3247,7 @@
         <v>453303.98</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>6424843.67</v>
+        <v>6424843.63</v>
       </c>
       <c r="G21" t="n">
         <v>30</v>
@@ -3279,10 +3279,10 @@
         </is>
       </c>
       <c r="E22" s="4" t="n">
-        <v>368019.88</v>
+        <v>368019.87</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>6321973.46</v>
+        <v>6321973.44</v>
       </c>
       <c r="G22" t="n">
         <v>31</v>
@@ -3308,7 +3308,7 @@
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>38197.67</v>
+        <v>38197.68</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
         <v>234075.1</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>5779856.55</v>
+        <v>5779856.56</v>
       </c>
       <c r="G23" t="n">
         <v>31</v>
@@ -3353,10 +3353,10 @@
         </is>
       </c>
       <c r="E24" s="4" t="n">
-        <v>216785.37</v>
+        <v>216785.36</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>5778059.78</v>
+        <v>5778059.73</v>
       </c>
       <c r="G24" t="n">
         <v>30</v>
@@ -3391,7 +3391,7 @@
         <v>324983.97</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>5473960.17</v>
+        <v>5473960.12</v>
       </c>
       <c r="G25" t="n">
         <v>30</v>
@@ -3415,7 +3415,7 @@
         </is>
       </c>
       <c r="C26" s="4" t="n">
-        <v>31074.37</v>
+        <v>31074.35</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3423,10 +3423,10 @@
         </is>
       </c>
       <c r="E26" s="4" t="n">
-        <v>230676.88</v>
+        <v>230676.89</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>5279335.28</v>
+        <v>5279335.24</v>
       </c>
       <c r="G26" t="n">
         <v>31</v>
@@ -3452,7 +3452,7 @@
         </is>
       </c>
       <c r="C27" s="4" t="n">
-        <v>56449.24</v>
+        <v>56449.23</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
         <v>379467.96</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>4919045.45</v>
+        <v>4919045.49</v>
       </c>
       <c r="G27" t="n">
         <v>31</v>
@@ -3489,7 +3489,7 @@
         </is>
       </c>
       <c r="C28" s="4" t="n">
-        <v>62388.79</v>
+        <v>62388.81</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3497,10 +3497,10 @@
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>209714.47</v>
+        <v>209714.46</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>4453253.35</v>
+        <v>4453253.37</v>
       </c>
       <c r="G28" t="n">
         <v>31</v>
@@ -3526,7 +3526,7 @@
         </is>
       </c>
       <c r="C29" s="4" t="n">
-        <v>7064.2</v>
+        <v>7064.21</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3537,7 +3537,7 @@
         <v>354620.42</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>4414442.89</v>
+        <v>4414442.96</v>
       </c>
       <c r="G29" t="n">
         <v>31</v>
@@ -3563,7 +3563,7 @@
         </is>
       </c>
       <c r="C30" s="4" t="n">
-        <v>8128.65</v>
+        <v>8128.67</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3571,10 +3571,10 @@
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>264709.99</v>
+        <v>264709.98</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>4165320.24</v>
+        <v>4165320.28</v>
       </c>
       <c r="G30" t="n">
         <v>31</v>
@@ -3600,7 +3600,7 @@
         </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>52869.85</v>
+        <v>52869.84</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3608,10 +3608,10 @@
         </is>
       </c>
       <c r="E31" s="4" t="n">
-        <v>131504.37</v>
+        <v>131504.36</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>4162272.24</v>
+        <v>4162272.23</v>
       </c>
       <c r="G31" t="n">
         <v>31</v>
@@ -3645,10 +3645,10 @@
         </is>
       </c>
       <c r="E32" s="4" t="n">
-        <v>172459.19</v>
+        <v>172459.18</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>3833710.33</v>
+        <v>3833710.35</v>
       </c>
       <c r="G32" t="n">
         <v>30</v>
@@ -3683,7 +3683,7 @@
         <v>339446.26</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>3640825.06</v>
+        <v>3640825.04</v>
       </c>
       <c r="G33" t="n">
         <v>16</v>
@@ -3718,7 +3718,7 @@
         <v>329129.97</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>3485209.8</v>
+        <v>3485209.79</v>
       </c>
       <c r="G34" t="n">
         <v>30</v>
@@ -3753,7 +3753,7 @@
         <v>216702.9</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>3384166.52</v>
+        <v>3384166.51</v>
       </c>
       <c r="G35" t="n">
         <v>30</v>
@@ -3777,7 +3777,7 @@
         </is>
       </c>
       <c r="C36" s="4" t="n">
-        <v>101216.44</v>
+        <v>101216.45</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3788,7 +3788,7 @@
         <v>78868.97</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>3327631.91</v>
+        <v>3327631.87</v>
       </c>
       <c r="G36" t="n">
         <v>31</v>
@@ -3814,7 +3814,7 @@
         </is>
       </c>
       <c r="C37" s="4" t="n">
-        <v>24051.53</v>
+        <v>24051.55</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3825,7 +3825,7 @@
         <v>186639.68</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>3178110.9</v>
+        <v>3178110.88</v>
       </c>
       <c r="G37" t="n">
         <v>31</v>
@@ -3862,7 +3862,7 @@
         <v>310797.54</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>3161788.4</v>
+        <v>3161788.41</v>
       </c>
       <c r="G38" t="n">
         <v>29</v>
@@ -3886,7 +3886,7 @@
         </is>
       </c>
       <c r="C39" s="4" t="n">
-        <v>6455.27</v>
+        <v>6455.26</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
         </is>
       </c>
       <c r="C40" s="4" t="n">
-        <v>71174.41</v>
+        <v>71174.42</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3931,10 +3931,10 @@
         </is>
       </c>
       <c r="E40" s="4" t="n">
-        <v>109171.55</v>
+        <v>109171.56</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>3018136.9</v>
+        <v>3018136.96</v>
       </c>
       <c r="G40" t="n">
         <v>31</v>
@@ -3968,10 +3968,10 @@
         </is>
       </c>
       <c r="E41" s="4" t="n">
-        <v>198428.16</v>
+        <v>198428.15</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>2763054.12</v>
+        <v>2763054.1</v>
       </c>
       <c r="G41" t="n">
         <v>29</v>
@@ -4003,7 +4003,7 @@
         </is>
       </c>
       <c r="E42" s="4" t="n">
-        <v>215903.38</v>
+        <v>215903.39</v>
       </c>
       <c r="F42" s="4" t="n">
         <v>2760230.11</v>
@@ -4030,7 +4030,7 @@
         </is>
       </c>
       <c r="C43" s="4" t="n">
-        <v>12756.5</v>
+        <v>12756.51</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4067,7 +4067,7 @@
         </is>
       </c>
       <c r="C44" s="4" t="n">
-        <v>43.69</v>
+        <v>43.68</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4078,13 +4078,13 @@
         <v>194467.17</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>2402569.32</v>
+        <v>2402569.34</v>
       </c>
       <c r="G44" t="n">
         <v>31</v>
       </c>
       <c r="H44" s="6" t="n">
-        <v>218.59</v>
+        <v>218.6</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -4115,7 +4115,7 @@
         <v>248105.42</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>2331977.99</v>
+        <v>2331977.97</v>
       </c>
       <c r="G45" t="n">
         <v>19</v>
@@ -4147,10 +4147,10 @@
         </is>
       </c>
       <c r="E46" s="4" t="n">
-        <v>97782.53</v>
+        <v>97782.52</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>2263306.34</v>
+        <v>2263306.38</v>
       </c>
       <c r="G46" t="n">
         <v>31</v>
@@ -4187,7 +4187,7 @@
         <v>125916.62</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>2232607.13</v>
+        <v>2232607.09</v>
       </c>
       <c r="G47" t="n">
         <v>30</v>
@@ -4222,7 +4222,7 @@
         <v>133398.27</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>2221868</v>
+        <v>2221868.05</v>
       </c>
       <c r="G48" t="n">
         <v>29</v>
@@ -4246,7 +4246,7 @@
         </is>
       </c>
       <c r="C49" s="4" t="n">
-        <v>5328.17</v>
+        <v>5328.19</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4254,10 +4254,10 @@
         </is>
       </c>
       <c r="E49" s="4" t="n">
-        <v>117358.63</v>
+        <v>117358.62</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>2181993.42</v>
+        <v>2181993.44</v>
       </c>
       <c r="G49" t="n">
         <v>31</v>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="C50" s="4" t="n">
-        <v>38042.7</v>
+        <v>38042.72</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="E50" s="4" t="n">
-        <v>87229.88</v>
+        <v>87229.87</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>2124191.36</v>
+        <v>2124191.42</v>
       </c>
       <c r="G50" t="n">
         <v>31</v>
@@ -4331,7 +4331,7 @@
         <v>203561.07</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>2123841.94</v>
+        <v>2123841.93</v>
       </c>
       <c r="G51" t="n">
         <v>17</v>
@@ -4366,7 +4366,7 @@
         <v>171589.35</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>2105596.49</v>
+        <v>2105596.52</v>
       </c>
       <c r="G52" t="n">
         <v>29</v>
@@ -4390,7 +4390,7 @@
         </is>
       </c>
       <c r="C53" s="4" t="n">
-        <v>24212.77</v>
+        <v>24212.76</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4401,7 +4401,7 @@
         <v>84591.58</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>1985119.59</v>
+        <v>1985119.62</v>
       </c>
       <c r="G53" t="n">
         <v>31</v>
@@ -4427,7 +4427,7 @@
         </is>
       </c>
       <c r="C54" s="4" t="n">
-        <v>11037.73</v>
+        <v>11037.7</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4438,7 +4438,7 @@
         <v>169994.38</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>1921433.25</v>
+        <v>1921433.21</v>
       </c>
       <c r="G54" t="n">
         <v>31</v>
@@ -4464,7 +4464,7 @@
         </is>
       </c>
       <c r="C55" s="4" t="n">
-        <v>21161.79</v>
+        <v>21161.81</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4475,7 +4475,7 @@
         <v>136765.06</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>1893076.39</v>
+        <v>1893076.44</v>
       </c>
       <c r="G55" t="n">
         <v>31</v>
@@ -4501,7 +4501,7 @@
         </is>
       </c>
       <c r="C56" s="4" t="n">
-        <v>520.12</v>
+        <v>520.09</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4512,13 +4512,13 @@
         <v>205774.52</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>1815324.49</v>
+        <v>1815324.43</v>
       </c>
       <c r="G56" t="n">
         <v>31</v>
       </c>
       <c r="H56" s="6" t="n">
-        <v>128.16</v>
+        <v>128.17</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -4546,10 +4546,10 @@
         </is>
       </c>
       <c r="E57" s="4" t="n">
-        <v>161459.16</v>
+        <v>161459.17</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>1706616.09</v>
+        <v>1706616.12</v>
       </c>
       <c r="G57" t="n">
         <v>16</v>
@@ -4573,7 +4573,7 @@
         </is>
       </c>
       <c r="C58" s="4" t="n">
-        <v>430.17</v>
+        <v>430.13</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4584,7 +4584,7 @@
         <v>53155.51</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>1703342.22</v>
+        <v>1703342.17</v>
       </c>
       <c r="G58" t="n">
         <v>31</v>
@@ -4610,7 +4610,7 @@
         </is>
       </c>
       <c r="C59" s="4" t="n">
-        <v>5717.51</v>
+        <v>5717.5</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4621,7 +4621,7 @@
         <v>69357.25</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>1682344.35</v>
+        <v>1682344.38</v>
       </c>
       <c r="G59" t="n">
         <v>31</v>
@@ -4658,7 +4658,7 @@
         <v>164486.45</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>1640887.26</v>
+        <v>1640887.28</v>
       </c>
       <c r="G60" t="n">
         <v>31</v>
@@ -4684,7 +4684,7 @@
         </is>
       </c>
       <c r="C61" s="4" t="n">
-        <v>10916.8</v>
+        <v>10916.82</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4695,7 +4695,7 @@
         <v>82301.45</v>
       </c>
       <c r="F61" s="4" t="n">
-        <v>1601003.77</v>
+        <v>1601003.86</v>
       </c>
       <c r="G61" t="n">
         <v>31</v>
@@ -4721,7 +4721,7 @@
         </is>
       </c>
       <c r="C62" s="4" t="n">
-        <v>27806.12</v>
+        <v>27806.08</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4732,7 +4732,7 @@
         <v>48558.85</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>1571391.79</v>
+        <v>1571391.77</v>
       </c>
       <c r="G62" t="n">
         <v>31</v>
@@ -4758,7 +4758,7 @@
         </is>
       </c>
       <c r="C63" s="4" t="n">
-        <v>5697.11</v>
+        <v>5697.08</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4766,10 +4766,10 @@
         </is>
       </c>
       <c r="E63" s="4" t="n">
-        <v>199221.34</v>
+        <v>199221.33</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>1535144.71</v>
+        <v>1535144.65</v>
       </c>
       <c r="G63" t="n">
         <v>31</v>
@@ -4803,7 +4803,7 @@
         </is>
       </c>
       <c r="E64" s="4" t="n">
-        <v>93931.03999999999</v>
+        <v>93931.03</v>
       </c>
       <c r="F64" s="4" t="n">
         <v>1527362.74</v>
@@ -4830,7 +4830,7 @@
         </is>
       </c>
       <c r="C65" s="4" t="n">
-        <v>39738.75</v>
+        <v>39738.73</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -4841,7 +4841,7 @@
         <v>57851.22</v>
       </c>
       <c r="F65" s="4" t="n">
-        <v>1488874.03</v>
+        <v>1488874.05</v>
       </c>
       <c r="G65" t="n">
         <v>31</v>
@@ -4867,7 +4867,7 @@
         </is>
       </c>
       <c r="C66" s="4" t="n">
-        <v>25191.51</v>
+        <v>25191.5</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -4878,7 +4878,7 @@
         <v>87422.21000000001</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>1414035.26</v>
+        <v>1414035.25</v>
       </c>
       <c r="G66" t="n">
         <v>31</v>
@@ -4904,7 +4904,7 @@
         </is>
       </c>
       <c r="C67" s="4" t="n">
-        <v>11366.36</v>
+        <v>11366.37</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -4912,10 +4912,10 @@
         </is>
       </c>
       <c r="E67" s="4" t="n">
-        <v>73981.36</v>
+        <v>73981.37</v>
       </c>
       <c r="F67" s="4" t="n">
-        <v>1409442.42</v>
+        <v>1409442.47</v>
       </c>
       <c r="G67" t="n">
         <v>31</v>
@@ -4941,7 +4941,7 @@
         </is>
       </c>
       <c r="C68" s="4" t="n">
-        <v>29745.09</v>
+        <v>29745.08</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -4952,7 +4952,7 @@
         <v>68524.09</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>1358334.53</v>
+        <v>1358334.55</v>
       </c>
       <c r="G68" t="n">
         <v>31</v>
@@ -4978,7 +4978,7 @@
         </is>
       </c>
       <c r="C69" s="4" t="n">
-        <v>7872.26</v>
+        <v>7872.27</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -4989,7 +4989,7 @@
         <v>61546.13</v>
       </c>
       <c r="F69" s="4" t="n">
-        <v>1330805.6</v>
+        <v>1330805.61</v>
       </c>
       <c r="G69" t="n">
         <v>31</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="C70" s="4" t="n">
-        <v>1997.38</v>
+        <v>1997.4</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5026,7 +5026,7 @@
         <v>95259.66</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>1216792.18</v>
+        <v>1216792.23</v>
       </c>
       <c r="G70" t="n">
         <v>31</v>
@@ -5063,7 +5063,7 @@
         <v>42035.59</v>
       </c>
       <c r="F71" s="4" t="n">
-        <v>1137291.54</v>
+        <v>1137291.52</v>
       </c>
       <c r="G71" t="n">
         <v>31</v>
@@ -5089,7 +5089,7 @@
         </is>
       </c>
       <c r="C72" s="4" t="n">
-        <v>21734.3</v>
+        <v>21734.32</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5097,10 +5097,10 @@
         </is>
       </c>
       <c r="E72" s="4" t="n">
-        <v>32891.96</v>
+        <v>32891.97</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>1117489.85</v>
+        <v>1117489.88</v>
       </c>
       <c r="G72" t="n">
         <v>31</v>
@@ -5137,7 +5137,7 @@
         <v>40120.6</v>
       </c>
       <c r="F73" s="4" t="n">
-        <v>1109651.4</v>
+        <v>1109651.39</v>
       </c>
       <c r="G73" t="n">
         <v>31</v>
@@ -5163,7 +5163,7 @@
         </is>
       </c>
       <c r="C74" s="4" t="n">
-        <v>13207.44</v>
+        <v>13207.45</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5200,7 +5200,7 @@
         </is>
       </c>
       <c r="C75" s="4" t="n">
-        <v>35815.67</v>
+        <v>35815.65</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5208,10 +5208,10 @@
         </is>
       </c>
       <c r="E75" s="4" t="n">
-        <v>28480.25</v>
+        <v>28480.24</v>
       </c>
       <c r="F75" s="4" t="n">
-        <v>1006403.46</v>
+        <v>1006403.41</v>
       </c>
       <c r="G75" t="n">
         <v>31</v>
@@ -5248,7 +5248,7 @@
         <v>83473.95</v>
       </c>
       <c r="F76" s="4" t="n">
-        <v>1005015.3</v>
+        <v>1005015.26</v>
       </c>
       <c r="G76" t="n">
         <v>31</v>
@@ -5285,7 +5285,7 @@
         <v>46325.16</v>
       </c>
       <c r="F77" s="4" t="n">
-        <v>962515.12</v>
+        <v>962515.16</v>
       </c>
       <c r="G77" t="n">
         <v>30</v>
@@ -5317,10 +5317,10 @@
         </is>
       </c>
       <c r="E78" s="4" t="n">
-        <v>35865.72</v>
+        <v>35865.73</v>
       </c>
       <c r="F78" s="4" t="n">
-        <v>935501.46</v>
+        <v>935501.5</v>
       </c>
       <c r="G78" t="n">
         <v>31</v>
@@ -5354,10 +5354,10 @@
         </is>
       </c>
       <c r="E79" s="4" t="n">
-        <v>46224.14</v>
+        <v>46224.15</v>
       </c>
       <c r="F79" s="4" t="n">
-        <v>909918.3100000001</v>
+        <v>909918.3199999999</v>
       </c>
       <c r="G79" t="n">
         <v>30</v>
@@ -5381,7 +5381,7 @@
         </is>
       </c>
       <c r="C80" s="4" t="n">
-        <v>16161.26</v>
+        <v>16161.24</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5392,7 +5392,7 @@
         <v>50741.15</v>
       </c>
       <c r="F80" s="4" t="n">
-        <v>906627.51</v>
+        <v>906627.4399999999</v>
       </c>
       <c r="G80" t="n">
         <v>31</v>
@@ -5418,7 +5418,7 @@
         </is>
       </c>
       <c r="C81" s="4" t="n">
-        <v>18197.21</v>
+        <v>18197.22</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5466,7 +5466,7 @@
         <v>87773.06</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v>871292.88</v>
+        <v>871292.89</v>
       </c>
       <c r="G82" t="n">
         <v>20</v>
@@ -5490,7 +5490,7 @@
         </is>
       </c>
       <c r="C83" s="4" t="n">
-        <v>4537.88</v>
+        <v>4537.9</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -5501,7 +5501,7 @@
         <v>65517.75</v>
       </c>
       <c r="F83" s="4" t="n">
-        <v>798805.04</v>
+        <v>798805.01</v>
       </c>
       <c r="G83" t="n">
         <v>31</v>
@@ -5538,7 +5538,7 @@
         <v>61182.36</v>
       </c>
       <c r="F84" s="4" t="n">
-        <v>731170.12</v>
+        <v>731170.11</v>
       </c>
       <c r="G84" t="n">
         <v>17</v>
@@ -5570,10 +5570,10 @@
         </is>
       </c>
       <c r="E85" s="4" t="n">
-        <v>37041.26</v>
+        <v>37041.25</v>
       </c>
       <c r="F85" s="4" t="n">
-        <v>657071.95</v>
+        <v>657071.9300000001</v>
       </c>
       <c r="G85" t="n">
         <v>29</v>
@@ -5608,7 +5608,7 @@
         <v>17025.74</v>
       </c>
       <c r="F86" s="4" t="n">
-        <v>604469.84</v>
+        <v>604469.79</v>
       </c>
       <c r="G86" t="n">
         <v>31</v>
@@ -5645,7 +5645,7 @@
         <v>43272</v>
       </c>
       <c r="F87" s="4" t="n">
-        <v>600116.8100000001</v>
+        <v>600116.88</v>
       </c>
       <c r="G87" t="n">
         <v>31</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="C88" s="4" t="n">
-        <v>4214.15</v>
+        <v>4214.12</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -5679,10 +5679,10 @@
         </is>
       </c>
       <c r="E88" s="4" t="n">
-        <v>37735.07</v>
+        <v>37735.06</v>
       </c>
       <c r="F88" s="4" t="n">
-        <v>587946.03</v>
+        <v>587945.99</v>
       </c>
       <c r="G88" t="n">
         <v>31</v>
@@ -5708,7 +5708,7 @@
         </is>
       </c>
       <c r="C89" s="4" t="n">
-        <v>690.84</v>
+        <v>690.85</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -5719,7 +5719,7 @@
         <v>52093.02</v>
       </c>
       <c r="F89" s="4" t="n">
-        <v>582966.0600000001</v>
+        <v>582966.0699999999</v>
       </c>
       <c r="G89" t="n">
         <v>31</v>
@@ -5745,7 +5745,7 @@
         </is>
       </c>
       <c r="C90" s="4" t="n">
-        <v>3755.4</v>
+        <v>3755.41</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="E90" s="4" t="n">
-        <v>33655.43</v>
+        <v>33655.42</v>
       </c>
       <c r="F90" s="4" t="n">
         <v>535955.65</v>
@@ -5793,7 +5793,7 @@
         <v>43524.05</v>
       </c>
       <c r="F91" s="4" t="n">
-        <v>502372.91</v>
+        <v>502372.93</v>
       </c>
       <c r="G91" t="n">
         <v>31</v>
@@ -5819,7 +5819,7 @@
         </is>
       </c>
       <c r="C92" s="4" t="n">
-        <v>9381.690000000001</v>
+        <v>9381.68</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -5830,7 +5830,7 @@
         <v>11533.35</v>
       </c>
       <c r="F92" s="4" t="n">
-        <v>498638.06</v>
+        <v>498638.04</v>
       </c>
       <c r="G92" t="n">
         <v>31</v>
@@ -5864,10 +5864,10 @@
         </is>
       </c>
       <c r="E93" s="4" t="n">
-        <v>18686.43</v>
+        <v>18686.44</v>
       </c>
       <c r="F93" s="4" t="n">
-        <v>466105.3</v>
+        <v>466105.35</v>
       </c>
       <c r="G93" t="n">
         <v>29</v>
@@ -5899,10 +5899,10 @@
         </is>
       </c>
       <c r="E94" s="4" t="n">
-        <v>18314.01</v>
+        <v>18314</v>
       </c>
       <c r="F94" s="4" t="n">
-        <v>425474.97</v>
+        <v>425474.96</v>
       </c>
       <c r="G94" t="n">
         <v>31</v>
@@ -5928,7 +5928,7 @@
         </is>
       </c>
       <c r="C95" s="4" t="n">
-        <v>4576.78</v>
+        <v>4576.79</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -5936,10 +5936,10 @@
         </is>
       </c>
       <c r="E95" s="4" t="n">
-        <v>31432.48</v>
+        <v>31432.47</v>
       </c>
       <c r="F95" s="4" t="n">
-        <v>420585.22</v>
+        <v>420585.21</v>
       </c>
       <c r="G95" t="n">
         <v>31</v>
@@ -5965,7 +5965,7 @@
         </is>
       </c>
       <c r="C96" s="4" t="n">
-        <v>12339.16</v>
+        <v>12339.17</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -5973,10 +5973,10 @@
         </is>
       </c>
       <c r="E96" s="4" t="n">
-        <v>13120.62</v>
+        <v>13120.63</v>
       </c>
       <c r="F96" s="4" t="n">
-        <v>417153.7</v>
+        <v>417153.75</v>
       </c>
       <c r="G96" t="n">
         <v>31</v>
@@ -6002,7 +6002,7 @@
         </is>
       </c>
       <c r="C97" s="4" t="n">
-        <v>3380.1</v>
+        <v>3380.12</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6013,7 +6013,7 @@
         <v>40098.23</v>
       </c>
       <c r="F97" s="4" t="n">
-        <v>414204.38</v>
+        <v>414204.4</v>
       </c>
       <c r="G97" t="n">
         <v>31</v>
@@ -6039,7 +6039,7 @@
         </is>
       </c>
       <c r="C98" s="4" t="n">
-        <v>5335.2</v>
+        <v>5335.18</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6050,7 +6050,7 @@
         <v>26516.5</v>
       </c>
       <c r="F98" s="4" t="n">
-        <v>389248.23</v>
+        <v>389248.18</v>
       </c>
       <c r="G98" t="n">
         <v>31</v>
@@ -6076,7 +6076,7 @@
         </is>
       </c>
       <c r="C99" s="4" t="n">
-        <v>2988.51</v>
+        <v>2988.54</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         <v>18970.97</v>
       </c>
       <c r="F99" s="4" t="n">
-        <v>371057.64</v>
+        <v>371057.65</v>
       </c>
       <c r="G99" t="n">
         <v>31</v>
@@ -6148,7 +6148,7 @@
         </is>
       </c>
       <c r="C101" s="4" t="n">
-        <v>4425.77</v>
+        <v>4425.78</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -6159,7 +6159,7 @@
         <v>16960.91</v>
       </c>
       <c r="F101" s="4" t="n">
-        <v>295198.37</v>
+        <v>295198.4</v>
       </c>
       <c r="G101" t="n">
         <v>31</v>
@@ -6185,7 +6185,7 @@
         </is>
       </c>
       <c r="C102" s="4" t="n">
-        <v>208.59</v>
+        <v>208.6</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -6193,7 +6193,7 @@
         </is>
       </c>
       <c r="E102" s="4" t="n">
-        <v>34503</v>
+        <v>34503.01</v>
       </c>
       <c r="F102" s="4" t="n">
         <v>294222.45</v>
@@ -6202,7 +6202,7 @@
         <v>31</v>
       </c>
       <c r="H102" s="6" t="n">
-        <v>102.31</v>
+        <v>102.3</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
@@ -6222,7 +6222,7 @@
         </is>
       </c>
       <c r="C103" s="4" t="n">
-        <v>2138.25</v>
+        <v>2138.23</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -6233,7 +6233,7 @@
         <v>15522.25</v>
       </c>
       <c r="F103" s="4" t="n">
-        <v>286862.94</v>
+        <v>286862.95</v>
       </c>
       <c r="G103" t="n">
         <v>31</v>
@@ -6259,7 +6259,7 @@
         </is>
       </c>
       <c r="C104" s="4" t="n">
-        <v>8082.04</v>
+        <v>8082.05</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -6267,10 +6267,10 @@
         </is>
       </c>
       <c r="E104" s="4" t="n">
-        <v>9322.440000000001</v>
+        <v>9322.450000000001</v>
       </c>
       <c r="F104" s="4" t="n">
-        <v>249395.56</v>
+        <v>249395.6</v>
       </c>
       <c r="G104" t="n">
         <v>31</v>
@@ -6296,7 +6296,7 @@
         </is>
       </c>
       <c r="C105" s="4" t="n">
-        <v>1887.86</v>
+        <v>1887.84</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -6304,10 +6304,10 @@
         </is>
       </c>
       <c r="E105" s="4" t="n">
-        <v>8841.58</v>
+        <v>8841.59</v>
       </c>
       <c r="F105" s="4" t="n">
-        <v>240796.32</v>
+        <v>240796.29</v>
       </c>
       <c r="G105" t="n">
         <v>31</v>
@@ -6344,7 +6344,7 @@
         <v>0.11</v>
       </c>
       <c r="F106" s="4" t="n">
-        <v>239500.77</v>
+        <v>239500.8</v>
       </c>
       <c r="G106" t="n">
         <v>30</v>
@@ -6368,7 +6368,7 @@
         </is>
       </c>
       <c r="C107" s="4" t="n">
-        <v>2730.94</v>
+        <v>2730.95</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -6376,10 +6376,10 @@
         </is>
       </c>
       <c r="E107" s="4" t="n">
-        <v>9687.059999999999</v>
+        <v>9687.07</v>
       </c>
       <c r="F107" s="4" t="n">
-        <v>232600.67</v>
+        <v>232600.68</v>
       </c>
       <c r="G107" t="n">
         <v>31</v>
@@ -6405,7 +6405,7 @@
         </is>
       </c>
       <c r="C108" s="4" t="n">
-        <v>899.42</v>
+        <v>899.4400000000001</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -6442,7 +6442,7 @@
         </is>
       </c>
       <c r="C109" s="4" t="n">
-        <v>2892.99</v>
+        <v>2892.97</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -6450,7 +6450,7 @@
         </is>
       </c>
       <c r="E109" s="4" t="n">
-        <v>18870.4</v>
+        <v>18870.39</v>
       </c>
       <c r="F109" s="4" t="n">
         <v>217986.17</v>
@@ -6479,7 +6479,7 @@
         </is>
       </c>
       <c r="C110" s="4" t="n">
-        <v>4072.92</v>
+        <v>4072.93</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -6490,7 +6490,7 @@
         <v>9454.43</v>
       </c>
       <c r="F110" s="4" t="n">
-        <v>183193.23</v>
+        <v>183193.22</v>
       </c>
       <c r="G110" t="n">
         <v>31</v>
@@ -6516,7 +6516,7 @@
         </is>
       </c>
       <c r="C111" s="4" t="n">
-        <v>1714.36</v>
+        <v>1714.38</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -6524,10 +6524,10 @@
         </is>
       </c>
       <c r="E111" s="4" t="n">
-        <v>20181.95</v>
+        <v>20181.94</v>
       </c>
       <c r="F111" s="4" t="n">
-        <v>174555.14</v>
+        <v>174555.1</v>
       </c>
       <c r="G111" t="n">
         <v>31</v>
@@ -6588,7 +6588,7 @@
         </is>
       </c>
       <c r="C113" s="4" t="n">
-        <v>741.9400000000001</v>
+        <v>741.95</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -6599,7 +6599,7 @@
         <v>4800.86</v>
       </c>
       <c r="F113" s="4" t="n">
-        <v>160713.62</v>
+        <v>160713.67</v>
       </c>
       <c r="G113" t="n">
         <v>31</v>
@@ -6636,7 +6636,7 @@
         <v>12317.42</v>
       </c>
       <c r="F114" s="4" t="n">
-        <v>152623.03</v>
+        <v>152623</v>
       </c>
       <c r="G114" t="n">
         <v>31</v>
@@ -6662,7 +6662,7 @@
         </is>
       </c>
       <c r="C115" s="4" t="n">
-        <v>312.02</v>
+        <v>312.05</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -6670,10 +6670,10 @@
         </is>
       </c>
       <c r="E115" s="4" t="n">
-        <v>15860.69</v>
+        <v>15860.7</v>
       </c>
       <c r="F115" s="4" t="n">
-        <v>147783.49</v>
+        <v>147783.54</v>
       </c>
       <c r="G115" t="n">
         <v>31</v>
@@ -6710,7 +6710,7 @@
         <v>7304.07</v>
       </c>
       <c r="F116" s="4" t="n">
-        <v>125109.68</v>
+        <v>125109.67</v>
       </c>
       <c r="G116" t="n">
         <v>30</v>
@@ -6734,7 +6734,7 @@
         </is>
       </c>
       <c r="C117" s="4" t="n">
-        <v>1537.32</v>
+        <v>1537.3</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -6745,7 +6745,7 @@
         <v>2787.64</v>
       </c>
       <c r="F117" s="4" t="n">
-        <v>116450.1</v>
+        <v>116450.06</v>
       </c>
       <c r="G117" t="n">
         <v>31</v>
@@ -6771,7 +6771,7 @@
         </is>
       </c>
       <c r="C118" s="4" t="n">
-        <v>2576</v>
+        <v>2576.01</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -6779,10 +6779,10 @@
         </is>
       </c>
       <c r="E118" s="4" t="n">
-        <v>8854.82</v>
+        <v>8854.809999999999</v>
       </c>
       <c r="F118" s="4" t="n">
-        <v>113196.25</v>
+        <v>113196.23</v>
       </c>
       <c r="G118" t="n">
         <v>31</v>
@@ -6819,7 +6819,7 @@
         <v>4680.29</v>
       </c>
       <c r="F119" s="4" t="n">
-        <v>104709.31</v>
+        <v>104709.28</v>
       </c>
       <c r="G119" t="n">
         <v>31</v>
@@ -6845,7 +6845,7 @@
         </is>
       </c>
       <c r="C120" s="4" t="n">
-        <v>810.41</v>
+        <v>810.4299999999999</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -6853,10 +6853,10 @@
         </is>
       </c>
       <c r="E120" s="4" t="n">
-        <v>8090.07</v>
+        <v>8090.08</v>
       </c>
       <c r="F120" s="4" t="n">
-        <v>94672.46000000001</v>
+        <v>94672.5</v>
       </c>
       <c r="G120" t="n">
         <v>31</v>
@@ -6882,7 +6882,7 @@
         </is>
       </c>
       <c r="C121" s="4" t="n">
-        <v>842.58</v>
+        <v>842.6</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -6893,7 +6893,7 @@
         <v>7252.59</v>
       </c>
       <c r="F121" s="4" t="n">
-        <v>93322.38</v>
+        <v>93322.39999999999</v>
       </c>
       <c r="G121" t="n">
         <v>31</v>
@@ -6919,7 +6919,7 @@
         </is>
       </c>
       <c r="C122" s="4" t="n">
-        <v>1656.33</v>
+        <v>1656.35</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -6930,7 +6930,7 @@
         <v>5772.79</v>
       </c>
       <c r="F122" s="4" t="n">
-        <v>84223.45</v>
+        <v>84223.42999999999</v>
       </c>
       <c r="G122" t="n">
         <v>31</v>
@@ -6956,7 +6956,7 @@
         </is>
       </c>
       <c r="C123" s="4" t="n">
-        <v>509</v>
+        <v>508.99</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -6964,10 +6964,10 @@
         </is>
       </c>
       <c r="E123" s="4" t="n">
-        <v>2621.69</v>
+        <v>2621.68</v>
       </c>
       <c r="F123" s="4" t="n">
-        <v>84058.7</v>
+        <v>84058.69</v>
       </c>
       <c r="G123" t="n">
         <v>31</v>
@@ -6993,7 +6993,7 @@
         </is>
       </c>
       <c r="C124" s="4" t="n">
-        <v>330.9</v>
+        <v>330.92</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
         <v>4847.59</v>
       </c>
       <c r="F124" s="4" t="n">
-        <v>78149.46000000001</v>
+        <v>78149.47</v>
       </c>
       <c r="G124" t="n">
         <v>31</v>
@@ -7030,7 +7030,7 @@
         </is>
       </c>
       <c r="C125" s="4" t="n">
-        <v>343.24</v>
+        <v>343.27</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -7067,7 +7067,7 @@
         </is>
       </c>
       <c r="C126" s="4" t="n">
-        <v>3486.46</v>
+        <v>3486.49</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -7078,7 +7078,7 @@
         <v>2439.6</v>
       </c>
       <c r="F126" s="4" t="n">
-        <v>43741.64</v>
+        <v>43741.67</v>
       </c>
       <c r="G126" t="n">
         <v>31</v>
@@ -7115,7 +7115,7 @@
         <v>707.27</v>
       </c>
       <c r="F127" s="4" t="n">
-        <v>7522.06</v>
+        <v>7522.13</v>
       </c>
       <c r="G127" t="n">
         <v>30</v>
@@ -7147,10 +7147,10 @@
         </is>
       </c>
       <c r="E128" s="4" t="n">
-        <v>122.96</v>
+        <v>122.95</v>
       </c>
       <c r="F128" s="4" t="n">
-        <v>3355.26</v>
+        <v>3355.25</v>
       </c>
       <c r="G128" t="n">
         <v>31</v>
@@ -7176,7 +7176,7 @@
         </is>
       </c>
       <c r="C129" s="4" t="n">
-        <v>25.57</v>
+        <v>25.59</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -7187,13 +7187,13 @@
         <v>26.11</v>
       </c>
       <c r="F129" s="4" t="n">
-        <v>883.5</v>
+        <v>883.5700000000001</v>
       </c>
       <c r="G129" t="n">
         <v>31</v>
       </c>
       <c r="H129" s="6" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
@@ -7224,7 +7224,7 @@
         <v>0</v>
       </c>
       <c r="F130" s="4" t="n">
-        <v>12.05</v>
+        <v>12.06</v>
       </c>
       <c r="G130" t="n">
         <v>4</v>

--- a/delivery130/03_Excel_Deliveries/9_Growth_Projection.xlsx
+++ b/delivery130/03_Excel_Deliveries/9_Growth_Projection.xlsx
@@ -20,8 +20,8 @@
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Annual'!$A$1:$G$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Window_Sensitivity'!$A$1:$H$6</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Window_Sensitivity'!$A$1:$H$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'By_Artist'!$A$1:$I$131</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'By_Artist'!$A$1:$I$131</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'By_Artist'!$A$1:$I$130</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'By_Artist'!$A$1:$I$130</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -483,14 +483,14 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Scope: 130 artists (first-submission cohort) x 31 quarters, Q1 2019 – Q3 2026</t>
+          <t>Scope: 129 artists (first-submission cohort) x 31 quarters, Q1 2019 – Q3 2026</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-31. Source: delivery130/04_Datasets — figures equal those cells.</t>
+          <t>Generated 2026-09-01. Source: delivery130/04_Datasets — figures equal those cells.</t>
         </is>
       </c>
     </row>
@@ -605,16 +605,16 @@
         <v>1872809.25</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>13378431.17</v>
+        <v>13378210.4</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>12392054.36</v>
+        <v>12391891.64</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>14421712.71</v>
+        <v>14421427.99</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>20067646755</v>
+        <v>20067315600</v>
       </c>
       <c r="H2" s="5" t="n">
         <v>92</v>
@@ -640,16 +640,16 @@
         <v>2323531.26</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>15117928.25</v>
+        <v>15117657.47</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>14003300.25</v>
+        <v>14003096.65</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>16296859.86</v>
+        <v>16296515.16</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>22676892375</v>
+        <v>22676486205</v>
       </c>
       <c r="H3" s="5" t="n">
         <v>108</v>
@@ -675,16 +675,16 @@
         <v>3218095.33</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>14804020.86</v>
+        <v>14803812.38</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>13712536.91</v>
+        <v>13712390.02</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>15958473.24</v>
+        <v>15958196.78</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>22206031290</v>
+        <v>22205718570</v>
       </c>
       <c r="H4" s="5" t="n">
         <v>117</v>
@@ -710,16 +710,16 @@
         <v>4262610.88</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>15157538.92</v>
+        <v>15157326.04</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>14039990.47</v>
+        <v>14039840.62</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>16339559.47</v>
+        <v>16339277.03</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>22736308380</v>
+        <v>22735989060</v>
       </c>
       <c r="H5" s="5" t="n">
         <v>118</v>
@@ -742,22 +742,22 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>3987687.47</v>
+        <v>3987655.09</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>14558691.36</v>
+        <v>14558485.95</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>13485295.28</v>
+        <v>13485150.48</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>15694012.37</v>
+        <v>15693740.08</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>21838037040</v>
+        <v>21837728925</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -777,22 +777,22 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>4568682.54</v>
+        <v>4568628.61</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>16451648.82</v>
+        <v>16451393.53</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>15238687.09</v>
+        <v>15238502</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>17734587.1</v>
+        <v>17734254.43</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>24677473230</v>
+        <v>24677090295</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -812,22 +812,22 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>5247262.97</v>
+        <v>5247193.78</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>16110048.17</v>
+        <v>16109859.85</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>14922272.28</v>
+        <v>14922148.15</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>17366347.64</v>
+        <v>17366088.35</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>24165072255</v>
+        <v>24164789775</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -847,22 +847,22 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>5432256.97</v>
+        <v>5432177.22</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>16494753.99</v>
+        <v>16494561.8</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>15278614.17</v>
+        <v>15278487.66</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>17781053.72</v>
+        <v>17780788.92</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>24742130985</v>
+        <v>24741842700</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -882,22 +882,22 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>5875940.51</v>
+        <v>5875850.44</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>15843075.43</v>
+        <v>15842889.81</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>14674983.14</v>
+        <v>14674860.68</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>17078555.73</v>
+        <v>17078300.29</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>23764613145</v>
+        <v>23764334715</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -917,22 +917,22 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>6943010.24</v>
+        <v>6942911.89</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>17903031.71</v>
+        <v>17902796.75</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>16583061.14</v>
+        <v>16582899.41</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>19299152.25</v>
+        <v>19298836.42</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>26854547565</v>
+        <v>26854195125</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -952,22 +952,22 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>8947657.74</v>
+        <v>8947551.25</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>17531294.68</v>
+        <v>17531131.7</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>16238731.86</v>
+        <v>16238635.65</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>18898426.29</v>
+        <v>18898189.35</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>26296942020</v>
+        <v>26296697550</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -987,22 +987,22 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>12461484.56</v>
+        <v>12461372.1</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>17949939.67</v>
+        <v>17949773.48</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>16626510.63</v>
+        <v>16626412.75</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>19349718.2</v>
+        <v>19349476.35</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>26924909505</v>
+        <v>26924660220</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1022,22 +1022,22 @@
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>12522069.94</v>
+        <v>12521951.57</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>17240769.3</v>
+        <v>17240608.57</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>15969626.6</v>
+        <v>15969531.56</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>18585245.06</v>
+        <v>18585011.56</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>25861153950</v>
+        <v>25860912855</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1057,22 +1057,22 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>13725219.54</v>
+        <v>13725097.33</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>19482457.23</v>
+        <v>19482248.16</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>18046037.38</v>
+        <v>18045904.56</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>21001745.09</v>
+        <v>21001451.66</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>29223685845</v>
+        <v>29223372240</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1092,22 +1092,22 @@
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>16545833.53</v>
+        <v>16545709.43</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>19077925.14</v>
+        <v>19077793.44</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>17671330.99</v>
+        <v>17671268.57</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>20565666.63</v>
+        <v>20565458.01</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>28616887710</v>
+        <v>28616690160</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1127,22 +1127,22 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>17741891.81</v>
+        <v>17741765.98</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>19533503.47</v>
+        <v>19533369.36</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>18093320.03</v>
+        <v>18093256.81</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>21056772.03</v>
+        <v>21056559.23</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>29300255205</v>
+        <v>29300054040</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1162,22 +1162,22 @@
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>19660327.37</v>
+        <v>19660200.27</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>18761769.29</v>
+        <v>18761639.28</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>17378484.95</v>
+        <v>17378423.12</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>20224856.2</v>
+        <v>20224650.51</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>28142653935</v>
+        <v>28142458920</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1197,22 +1197,22 @@
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>23324978.72</v>
+        <v>23324850.92</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>21201221.44</v>
+        <v>21201044.67</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>19638079.02</v>
+        <v>19637981.49</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>22854542.58</v>
+        <v>22854277.95</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>31801832160</v>
+        <v>31801567005</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1232,22 +1232,22 @@
         </is>
       </c>
       <c r="C20" s="4" t="n">
-        <v>20941938.91</v>
+        <v>20941810.56</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>20761001.08</v>
+        <v>20760907.44</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>19230315.61</v>
+        <v>19230293.71</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>22379992.79</v>
+        <v>22379819.32</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>31141501620</v>
+        <v>31141361160</v>
       </c>
       <c r="H20" s="5" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1267,22 +1267,22 @@
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>21429816.82</v>
+        <v>21429687.92</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>21256771.03</v>
+        <v>21256675.97</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>19689533</v>
+        <v>19689511.33</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>22914424.05</v>
+        <v>22914247.32</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>31885156545</v>
+        <v>31885013955</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1302,22 +1302,22 @@
         </is>
       </c>
       <c r="C22" s="4" t="n">
-        <v>20850286.89</v>
+        <v>20850157.48</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>20416953.6</v>
+        <v>20416860.98</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>18911634.37</v>
+        <v>18911612.34</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>22009115.68</v>
+        <v>22008944.51</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>30625430400</v>
+        <v>30625291470</v>
       </c>
       <c r="H22" s="5" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1337,22 +1337,22 @@
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>23032148.22</v>
+        <v>23032018.33</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>23071616.96</v>
+        <v>23071479.8</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>21370572.36</v>
+        <v>21370517.36</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>24870795.94</v>
+        <v>24870567.48</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>34607425440</v>
+        <v>34607219700</v>
       </c>
       <c r="H23" s="5" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1372,22 +1372,22 @@
         </is>
       </c>
       <c r="C24" s="4" t="n">
-        <v>23051208.66</v>
+        <v>23051208.35</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>22592559.86</v>
+        <v>22592512.03</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>20926835.6</v>
+        <v>20926861.85</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>24354380.84</v>
+        <v>24354250.35</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>33888839790</v>
+        <v>33888768045</v>
       </c>
       <c r="H24" s="5" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1407,22 +1407,22 @@
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>23152246.24</v>
+        <v>23152245.93</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>23132067.19</v>
+        <v>23132019.11</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>21426565.67</v>
+        <v>21426593.36</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>24935960.22</v>
+        <v>24935827.57</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>34698100785</v>
+        <v>34698028665</v>
       </c>
       <c r="H25" s="5" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1442,22 +1442,22 @@
         </is>
       </c>
       <c r="C26" s="4" t="n">
-        <v>20985647.56</v>
+        <v>20985647.25</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>22218160.13</v>
+        <v>22218112.51</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>20580039.95</v>
+        <v>20580065.22</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>23950784.53</v>
+        <v>23950655.58</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>33327240195</v>
+        <v>33327168765</v>
       </c>
       <c r="H26" s="5" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1477,22 +1477,22 @@
         </is>
       </c>
       <c r="C27" s="4" t="n">
-        <v>24001481.5</v>
+        <v>24001481.19</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>25107020.86</v>
+        <v>25106931.69</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>23255908.2</v>
+        <v>23255904.01</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>27064925.43</v>
+        <v>27064741.59</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>37660531290</v>
+        <v>37660397535</v>
       </c>
       <c r="H27" s="5" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1512,22 +1512,22 @@
         </is>
       </c>
       <c r="C28" s="4" t="n">
-        <v>23834738.58</v>
+        <v>23834738.27</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>24585700.81</v>
+        <v>24585707.6</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>22773024.49</v>
+        <v>22773107.56</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>26502951.6</v>
+        <v>26502873.03</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>36878551215</v>
+        <v>36878561400</v>
       </c>
       <c r="H28" s="5" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -1547,22 +1547,22 @@
         </is>
       </c>
       <c r="C29" s="4" t="n">
-        <v>24891805.71</v>
+        <v>24891805.4</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>25172804.09</v>
+        <v>25172812</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>23316841.3</v>
+        <v>23316927.24</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>27135838.58</v>
+        <v>27135759.17</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>37759206135</v>
+        <v>37759218000</v>
       </c>
       <c r="H29" s="5" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -1582,22 +1582,22 @@
         </is>
       </c>
       <c r="C30" s="4" t="n">
-        <v>25010048.03</v>
+        <v>25010047.72</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>24178271.11</v>
+        <v>24178277.15</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>22395634.13</v>
+        <v>22395715.24</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>26063749.58</v>
+        <v>26063671.63</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>36267406665</v>
+        <v>36267415725</v>
       </c>
       <c r="H30" s="5" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -1617,22 +1617,22 @@
         </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>28565229.17</v>
+        <v>28565091.87</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>27321990.38</v>
+        <v>27321958.73</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>25307570.48</v>
+        <v>25307626.49</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>29452623.48</v>
+        <v>29452493.91</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>40982985570</v>
+        <v>40982938095</v>
       </c>
       <c r="H31" s="5" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -1652,22 +1652,22 @@
         </is>
       </c>
       <c r="C32" s="4" t="n">
-        <v>28556269.83</v>
+        <v>28556131.57</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>26754678.88</v>
+        <v>26754750.3</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>24782086.23</v>
+        <v>24782235.94</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>28841071.7</v>
+        <v>28841055.21</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>40132018320</v>
+        <v>40132125450</v>
       </c>
       <c r="H32" s="5" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -1688,16 +1688,16 @@
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" s="4" t="n">
-        <v>27393577.07</v>
+        <v>27393651.24</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>25373879.17</v>
+        <v>25374033.42</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>29529792.67</v>
+        <v>29529776.92</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>41090365605</v>
+        <v>41090476860</v>
       </c>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
@@ -1719,16 +1719,16 @@
       </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" s="4" t="n">
-        <v>26311305.28</v>
+        <v>26311374.83</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>24371402.07</v>
+        <v>24371548.66</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>28363122.78</v>
+        <v>28363105.83</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>39466957920</v>
+        <v>39467062245</v>
       </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
@@ -1750,16 +1750,16 @@
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" s="4" t="n">
-        <v>29732366.99</v>
+        <v>29732403.7</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>27540232.71</v>
+        <v>27540359.57</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>32050966.93</v>
+        <v>32050902.63</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>44598550485</v>
+        <v>44598605550</v>
       </c>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
@@ -1781,16 +1781,16 @@
       </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" s="4" t="n">
-        <v>29115006.64</v>
+        <v>29115154.03</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>26968389.65</v>
+        <v>26968617.1</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>31385463.36</v>
+        <v>31385520.54</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>43672509960</v>
+        <v>43672731045</v>
       </c>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
@@ -1812,16 +1812,16 @@
       </c>
       <c r="C37" t="inlineStr"/>
       <c r="D37" s="4" t="n">
-        <v>29810269.14</v>
+        <v>29810421.19</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>27612391.23</v>
+        <v>27612625.16</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>32134944.07</v>
+        <v>32135003.84</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>44715403710</v>
+        <v>44715631785</v>
       </c>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
@@ -1843,16 +1843,16 @@
       </c>
       <c r="C38" t="inlineStr"/>
       <c r="D38" s="4" t="n">
-        <v>28632518.12</v>
+        <v>28632662.33</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>26521474.48</v>
+        <v>26521697.47</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>30865349.26</v>
+        <v>30865404.68</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>42948777180</v>
+        <v>42948993495</v>
       </c>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
@@ -1874,16 +1874,16 @@
       </c>
       <c r="C39" t="inlineStr"/>
       <c r="D39" s="4" t="n">
-        <v>32355389.72</v>
+        <v>32355507.11</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>29969862.91</v>
+        <v>29970072.68</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>34878539.14</v>
+        <v>34878552.65</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>48533084580</v>
+        <v>48533260665</v>
       </c>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
@@ -1905,16 +1905,16 @@
       </c>
       <c r="C40" t="inlineStr"/>
       <c r="D40" s="4" t="n">
-        <v>31683565.15</v>
+        <v>31683801.38</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>29347571.21</v>
+        <v>29347888.96</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>34154324.11</v>
+        <v>34154468.07</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>47525347725</v>
+        <v>47525702070</v>
       </c>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
@@ -1993,10 +1993,10 @@
         <v>11677046.72</v>
       </c>
       <c r="C2" s="4" t="n">
-        <v>58457919.2</v>
+        <v>58457006.29</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>87686878800</v>
+        <v>87685509435</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -2015,13 +2015,13 @@
         <v>2020</v>
       </c>
       <c r="B3" s="4" t="n">
-        <v>19235889.95</v>
+        <v>19235654.7</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>63615142.34</v>
+        <v>63614301.13</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>95422713510</v>
+        <v>95421451695</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -2040,13 +2040,13 @@
         <v>2021</v>
       </c>
       <c r="B4" s="4" t="n">
-        <v>34228093.05</v>
+        <v>34227685.68</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>69227341.48999999</v>
+        <v>69226591.73999999</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>103841012235</v>
+        <v>103839887610</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -2065,13 +2065,13 @@
         <v>2022</v>
       </c>
       <c r="B5" s="4" t="n">
-        <v>60535014.82</v>
+        <v>60534524.31</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>75334655.14</v>
+        <v>75334019.53</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>113001982710</v>
+        <v>113001029295</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -2090,13 +2090,13 @@
         <v>2023</v>
       </c>
       <c r="B6" s="4" t="n">
-        <v>85357061.81999999</v>
+        <v>85356549.67</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>81980762.84</v>
+        <v>81980267.36</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>122971144260</v>
+        <v>122970401040</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -2115,13 +2115,13 @@
         <v>2024</v>
       </c>
       <c r="B7" s="4" t="n">
-        <v>90085890.01000001</v>
+        <v>90085630.09</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>89213197.61</v>
+        <v>89212871.92</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>133819796415</v>
+        <v>133819307880</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -2140,13 +2140,13 @@
         <v>2025</v>
       </c>
       <c r="B8" s="4" t="n">
-        <v>93713673.34999999</v>
+        <v>93713672.11</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>97083685.89</v>
+        <v>97083563.8</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>145625528835</v>
+        <v>145625345700</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -2165,13 +2165,13 @@
         <v>2026</v>
       </c>
       <c r="B9" s="4" t="n">
-        <v>82131547.03</v>
+        <v>82131271.16</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>105648517.44</v>
+        <v>105648637.42</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>158472776160</v>
+        <v>158472956130</v>
       </c>
       <c r="E9" t="n">
         <v>1</v>
@@ -2193,10 +2193,10 @@
         <v>0</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>114968948.05</v>
+        <v>114969353.75</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>172453422075</v>
+        <v>172454030625</v>
       </c>
       <c r="E10" t="n">
         <v>4</v>
@@ -2218,10 +2218,10 @@
         <v>0</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>92671472.98999999</v>
+        <v>92671970.81999999</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>139007209485</v>
+        <v>139007956230</v>
       </c>
       <c r="E11" t="n">
         <v>3</v>
@@ -2476,7 +2476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I131"/>
+  <dimension ref="A1:I130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -5605,16 +5605,16 @@
         </is>
       </c>
       <c r="E86" s="4" t="n">
-        <v>17025.74</v>
+        <v>16888.75</v>
       </c>
       <c r="F86" s="4" t="n">
-        <v>604469.79</v>
+        <v>602295.47</v>
       </c>
       <c r="G86" t="n">
         <v>31</v>
       </c>
       <c r="H86" s="6" t="n">
-        <v>7.06</v>
+        <v>6.94</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
@@ -7236,43 +7236,8 @@
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>Odunsi</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>Q1_2019</t>
-        </is>
-      </c>
-      <c r="C131" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>Q2_2026</t>
-        </is>
-      </c>
-      <c r="E131" s="4" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="F131" s="4" t="n">
-        <v>7.99</v>
-      </c>
-      <c r="G131" t="n">
-        <v>27</v>
-      </c>
-      <c r="H131" t="inlineStr"/>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>UNK</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:I131"/>
+  <autoFilter ref="A1:I130"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/delivery130/03_Excel_Deliveries/9_Growth_Projection.xlsx
+++ b/delivery130/03_Excel_Deliveries/9_Growth_Projection.xlsx
@@ -605,16 +605,16 @@
         <v>1872809.25</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>13378210.4</v>
+        <v>13416173.56</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>12391891.64</v>
+        <v>12423050.36</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>14421427.99</v>
+        <v>14466833.65</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>20067315600</v>
+        <v>20124260340</v>
       </c>
       <c r="H2" s="5" t="n">
         <v>92</v>
@@ -640,16 +640,16 @@
         <v>2323531.26</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>15117657.47</v>
+        <v>15160578.02</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>14003096.65</v>
+        <v>14038326.45</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>16296515.16</v>
+        <v>16347847.56</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>22676486205</v>
+        <v>22740867030</v>
       </c>
       <c r="H3" s="5" t="n">
         <v>108</v>
@@ -675,16 +675,16 @@
         <v>3218095.33</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>14803812.38</v>
+        <v>14838831.44</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>13712390.02</v>
+        <v>13740396.95</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>15958196.78</v>
+        <v>16000904.06</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>22205718570</v>
+        <v>22258247160</v>
       </c>
       <c r="H4" s="5" t="n">
         <v>117</v>
@@ -710,16 +710,16 @@
         <v>4262610.88</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>15157326.04</v>
+        <v>15174640.78</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>14039840.62</v>
+        <v>14051348.23</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>16339277.03</v>
+        <v>16363011.62</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>22735989060</v>
+        <v>22761961170</v>
       </c>
       <c r="H5" s="5" t="n">
         <v>118</v>
@@ -742,19 +742,19 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>3987655.09</v>
+        <v>3987687.25</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>14558485.95</v>
+        <v>14592925.06</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>13485150.48</v>
+        <v>13512693.62</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>15693740.08</v>
+        <v>15735740.03</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>21837728925</v>
+        <v>21889387590</v>
       </c>
       <c r="H6" s="5" t="n">
         <v>118</v>
@@ -777,19 +777,19 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>4568628.61</v>
+        <v>4568682.3</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>16451393.53</v>
+        <v>16490333.7</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>15238502</v>
+        <v>15269647.86</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>17734254.43</v>
+        <v>17781740.32</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>24677090295</v>
+        <v>24735500550</v>
       </c>
       <c r="H7" s="5" t="n">
         <v>118</v>
@@ -812,19 +812,19 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>5247193.78</v>
+        <v>5247262.71</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>16109859.85</v>
+        <v>16140366.27</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>14922148.15</v>
+        <v>14945586.54</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>17366088.35</v>
+        <v>17404365.92</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>24164789775</v>
+        <v>24210549405</v>
       </c>
       <c r="H8" s="5" t="n">
         <v>118</v>
@@ -847,19 +847,19 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>5432177.22</v>
+        <v>5450699.72</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>16494561.8</v>
+        <v>16505629.92</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>15278487.66</v>
+        <v>15283811.79</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>17780788.92</v>
+        <v>17798234.44</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>24741842700</v>
+        <v>24758444880</v>
       </c>
       <c r="H9" s="5" t="n">
         <v>119</v>
@@ -882,19 +882,19 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>5875850.44</v>
+        <v>5875940.25</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>15842889.81</v>
+        <v>15872891.1</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>14674860.68</v>
+        <v>14697911.03</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>17078300.29</v>
+        <v>17115943.97</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>23764334715</v>
+        <v>23809336650</v>
       </c>
       <c r="H10" s="5" t="n">
         <v>120</v>
@@ -917,19 +917,19 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>6942911.89</v>
+        <v>6943009.98</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>17902796.75</v>
+        <v>17936724.12</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>16582899.41</v>
+        <v>16608970.2</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>19298836.42</v>
+        <v>19341401.84</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>26854195125</v>
+        <v>26905086180</v>
       </c>
       <c r="H11" s="5" t="n">
         <v>120</v>
@@ -952,19 +952,19 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>8947551.25</v>
+        <v>8947657.449999999</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>17531131.7</v>
+        <v>17556060.56</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>16238635.65</v>
+        <v>16256485.01</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>18898189.35</v>
+        <v>18930927.4</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>26296697550</v>
+        <v>26334090840</v>
       </c>
       <c r="H12" s="5" t="n">
         <v>120</v>
@@ -987,19 +987,19 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>12461372.1</v>
+        <v>12461484.25</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>17949773.48</v>
+        <v>17953362</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>16626412.75</v>
+        <v>16624376.48</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>19349476.35</v>
+        <v>19359342.68</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>26924660220</v>
+        <v>26930043000</v>
       </c>
       <c r="H13" s="5" t="n">
         <v>121</v>
@@ -1022,19 +1022,19 @@
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>12521951.57</v>
+        <v>12548977.87</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>17240608.57</v>
+        <v>17265124.76</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>15969531.56</v>
+        <v>15987085.53</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>18585011.56</v>
+        <v>18617207.56</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>25860912855</v>
+        <v>25897687140</v>
       </c>
       <c r="H14" s="5" t="n">
         <v>122</v>
@@ -1057,19 +1057,19 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>13725097.33</v>
+        <v>13725219.23</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>19482248.16</v>
+        <v>19509979.48</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>18045904.56</v>
+        <v>18065766.4</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>21001451.66</v>
+        <v>21037863.47</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>29223372240</v>
+        <v>29264969220</v>
       </c>
       <c r="H15" s="5" t="n">
         <v>122</v>
@@ -1092,19 +1092,19 @@
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>16545709.43</v>
+        <v>16545833.22</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>19077793.44</v>
+        <v>19095927.39</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>17671268.57</v>
+        <v>17682364.23</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>20565458.01</v>
+        <v>20591385.73</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>28616690160</v>
+        <v>28643891085</v>
       </c>
       <c r="H16" s="5" t="n">
         <v>125</v>
@@ -1127,19 +1127,19 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>17741765.98</v>
+        <v>17741891.5</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>19533369.36</v>
+        <v>19528076.7</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>18093256.81</v>
+        <v>18082523.98</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>21056559.23</v>
+        <v>21057377.93</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>29300054040</v>
+        <v>29292115050</v>
       </c>
       <c r="H17" s="5" t="n">
         <v>127</v>
@@ -1162,19 +1162,19 @@
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>19660200.27</v>
+        <v>19660327.06</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>18761639.28</v>
+        <v>18779473.2</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>17378423.12</v>
+        <v>17389335.35</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>20224650.51</v>
+        <v>20250149.08</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>28142458920</v>
+        <v>28169209800</v>
       </c>
       <c r="H18" s="5" t="n">
         <v>127</v>
@@ -1197,19 +1197,19 @@
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>23324850.92</v>
+        <v>23324978.41</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>21201044.67</v>
+        <v>21221227.29</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>19637981.49</v>
+        <v>19650340.25</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>22854277.95</v>
+        <v>22883124.14</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>31801567005</v>
+        <v>31831840935</v>
       </c>
       <c r="H19" s="5" t="n">
         <v>127</v>
@@ -1232,19 +1232,19 @@
         </is>
       </c>
       <c r="C20" s="4" t="n">
-        <v>20941810.56</v>
+        <v>20941938.6</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>20760907.44</v>
+        <v>20770858.1</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>19230293.71</v>
+        <v>19233309.33</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>22379819.32</v>
+        <v>22397485.21</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>31141361160</v>
+        <v>31156287150</v>
       </c>
       <c r="H20" s="5" t="n">
         <v>127</v>
@@ -1267,19 +1267,19 @@
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>21429687.92</v>
+        <v>21429816.51</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>21256675.97</v>
+        <v>21240911.84</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>19689511.33</v>
+        <v>19668567.66</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>22914247.32</v>
+        <v>22904350.24</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>31885013955</v>
+        <v>31861367760</v>
       </c>
       <c r="H21" s="5" t="n">
         <v>127</v>
@@ -1302,19 +1302,19 @@
         </is>
       </c>
       <c r="C22" s="4" t="n">
-        <v>20850157.48</v>
+        <v>20850286.58</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>20416860.98</v>
+        <v>20426647.27</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>18911612.34</v>
+        <v>18914578.47</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>22008944.51</v>
+        <v>22026318.21</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>30625291470</v>
+        <v>30639970905</v>
       </c>
       <c r="H22" s="5" t="n">
         <v>127</v>
@@ -1337,19 +1337,19 @@
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>23032018.33</v>
+        <v>23032147.91</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>23071479.8</v>
+        <v>23082571.06</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>21370517.36</v>
+        <v>21373899.3</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>24870567.48</v>
+        <v>24890235.23</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>34607219700</v>
+        <v>34623856590</v>
       </c>
       <c r="H23" s="5" t="n">
         <v>127</v>
@@ -1375,16 +1375,16 @@
         <v>23051208.35</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>22592512.03</v>
+        <v>22592699.36</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>20926861.85</v>
+        <v>20920290.01</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>24354250.35</v>
+        <v>24362000.22</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>33888768045</v>
+        <v>33889049040</v>
       </c>
       <c r="H24" s="5" t="n">
         <v>127</v>
@@ -1407,19 +1407,19 @@
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>23152245.93</v>
+        <v>23154211.86</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>23132019.11</v>
+        <v>23103982.17</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>21426593.36</v>
+        <v>21393725.46</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>24935827.57</v>
+        <v>24913323.1</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>34698028665</v>
+        <v>34655973255</v>
       </c>
       <c r="H25" s="5" t="n">
         <v>128</v>
@@ -1445,16 +1445,16 @@
         <v>20985647.25</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>22218112.51</v>
+        <v>22218297.31</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>20580065.22</v>
+        <v>20573602.82</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>23950655.58</v>
+        <v>23958277.64</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>33327168765</v>
+        <v>33327445965</v>
       </c>
       <c r="H26" s="5" t="n">
         <v>129</v>
@@ -1480,16 +1480,16 @@
         <v>24001481.19</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>25106931.69</v>
+        <v>25107175.92</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>23255904.01</v>
+        <v>23248634.14</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>27064741.59</v>
+        <v>27073392.86</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>37660397535</v>
+        <v>37660763880</v>
       </c>
       <c r="H27" s="5" t="n">
         <v>129</v>
@@ -1515,16 +1515,16 @@
         <v>23834738.27</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>24585707.6</v>
+        <v>24574336.88</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>22773107.56</v>
+        <v>22755238.15</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>26502873.03</v>
+        <v>26498825.61</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>36878561400</v>
+        <v>36861505320</v>
       </c>
       <c r="H28" s="5" t="n">
         <v>129</v>
@@ -1547,19 +1547,19 @@
         </is>
       </c>
       <c r="C29" s="4" t="n">
-        <v>24891805.4</v>
+        <v>24798685.61</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>25172812</v>
+        <v>25130465.02</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>23316927.24</v>
+        <v>23270199.29</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>27135759.17</v>
+        <v>27098505.8</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>37759218000</v>
+        <v>37695697530</v>
       </c>
       <c r="H29" s="5" t="n">
         <v>128</v>
@@ -1585,16 +1585,16 @@
         <v>25010047.72</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>24178277.15</v>
+        <v>24167095.5</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>22395715.24</v>
+        <v>22378142.54</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>26063671.63</v>
+        <v>26059691.96</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>36267415725</v>
+        <v>36250643250</v>
       </c>
       <c r="H30" s="5" t="n">
         <v>128</v>
@@ -1617,19 +1617,19 @@
         </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>28565091.87</v>
+        <v>28565228.86</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>27321958.73</v>
+        <v>27309361.73</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>25307626.49</v>
+        <v>25287804.63</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>29452493.91</v>
+        <v>29448038.32</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>40982938095</v>
+        <v>40964042595</v>
       </c>
       <c r="H31" s="5" t="n">
         <v>127</v>
@@ -1652,19 +1652,19 @@
         </is>
       </c>
       <c r="C32" s="4" t="n">
-        <v>28556131.57</v>
+        <v>28556269.52</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>26754750.3</v>
+        <v>26729786.62</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>24782235.94</v>
+        <v>24751132.18</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>28841055.21</v>
+        <v>28823074.97</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>40132125450</v>
+        <v>40094679930</v>
       </c>
       <c r="H32" s="5" t="n">
         <v>127</v>
@@ -1688,16 +1688,16 @@
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" s="4" t="n">
-        <v>27393651.24</v>
+        <v>27334693.55</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>25374033.42</v>
+        <v>25311261.28</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>29529776.92</v>
+        <v>29475353.95</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>41090476860</v>
+        <v>41002040325</v>
       </c>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
@@ -1719,16 +1719,16 @@
       </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" s="4" t="n">
-        <v>26311374.83</v>
+        <v>26286825.52</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>24371548.66</v>
+        <v>24340960.98</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>28363105.83</v>
+        <v>28345424.29</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>39467062245</v>
+        <v>39430238280</v>
       </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
@@ -1750,16 +1750,16 @@
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" s="4" t="n">
-        <v>29732403.7</v>
+        <v>29704704.35</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>27540359.57</v>
+        <v>27505833.63</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>32050902.63</v>
+        <v>32030967.28</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>44598605550</v>
+        <v>44557056525</v>
       </c>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
@@ -1781,16 +1781,16 @@
       </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" s="4" t="n">
-        <v>29115154.03</v>
+        <v>29074293.89</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>26968617.1</v>
+        <v>26922088.88</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>31385520.54</v>
+        <v>31351187.52</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>43672731045</v>
+        <v>43611440835</v>
       </c>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
@@ -1812,16 +1812,16 @@
       </c>
       <c r="C37" t="inlineStr"/>
       <c r="D37" s="4" t="n">
-        <v>29810421.19</v>
+        <v>29732258.06</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>27612625.16</v>
+        <v>27531347.7</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>32135003.84</v>
+        <v>32060678.81</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>44715631785</v>
+        <v>44598387090</v>
       </c>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
@@ -1843,16 +1843,16 @@
       </c>
       <c r="C38" t="inlineStr"/>
       <c r="D38" s="4" t="n">
-        <v>28632662.33</v>
+        <v>28592480.05</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>26521697.47</v>
+        <v>26475940.99</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>30865404.68</v>
+        <v>30831641.42</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>42948993495</v>
+        <v>42888720075</v>
       </c>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
@@ -1874,16 +1874,16 @@
       </c>
       <c r="C39" t="inlineStr"/>
       <c r="D39" s="4" t="n">
-        <v>32355507.11</v>
+        <v>32310145.86</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>29970072.68</v>
+        <v>29918409.09</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>34878552.65</v>
+        <v>34840448.59</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>48533260665</v>
+        <v>48465218790</v>
       </c>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
@@ -1905,16 +1905,16 @@
       </c>
       <c r="C40" t="inlineStr"/>
       <c r="D40" s="4" t="n">
-        <v>31683801.38</v>
+        <v>31624441.21</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>29347888.96</v>
+        <v>29283463.26</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>34154468.07</v>
+        <v>34101044.39</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>47525702070</v>
+        <v>47436661815</v>
       </c>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
@@ -1993,10 +1993,10 @@
         <v>11677046.72</v>
       </c>
       <c r="C2" s="4" t="n">
-        <v>58457006.29</v>
+        <v>58590223.8</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>87685509435</v>
+        <v>87885335700</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -2015,13 +2015,13 @@
         <v>2020</v>
       </c>
       <c r="B3" s="4" t="n">
-        <v>19235654.7</v>
+        <v>19254331.98</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>63614301.13</v>
+        <v>63729254.95</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>95421451695</v>
+        <v>95593882425</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -2040,13 +2040,13 @@
         <v>2021</v>
       </c>
       <c r="B4" s="4" t="n">
-        <v>34227685.68</v>
+        <v>34228091.93</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>69226591.73999999</v>
+        <v>69319037.78</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>103839887610</v>
+        <v>103978556670</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -2065,13 +2065,13 @@
         <v>2022</v>
       </c>
       <c r="B5" s="4" t="n">
-        <v>60534524.31</v>
+        <v>60561921.82</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>75334019.53</v>
+        <v>75399108.33</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>113001029295</v>
+        <v>113098662495</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -2090,13 +2090,13 @@
         <v>2023</v>
       </c>
       <c r="B6" s="4" t="n">
-        <v>85356549.67</v>
+        <v>85357060.58</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>81980267.36</v>
+        <v>82012470.43000001</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>122970401040</v>
+        <v>123018705645</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -2115,13 +2115,13 @@
         <v>2024</v>
       </c>
       <c r="B7" s="4" t="n">
-        <v>90085630.09</v>
+        <v>90087854.7</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>89212871.92</v>
+        <v>89205899.86</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>133819307880</v>
+        <v>133808849790</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -2140,13 +2140,13 @@
         <v>2025</v>
       </c>
       <c r="B8" s="4" t="n">
-        <v>93713672.11</v>
+        <v>93620552.31999999</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>97083563.8</v>
+        <v>97030275.13</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>145625345700</v>
+        <v>145545412695</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -2165,13 +2165,13 @@
         <v>2026</v>
       </c>
       <c r="B9" s="4" t="n">
-        <v>82131271.16</v>
+        <v>82131546.09999999</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>105648637.42</v>
+        <v>105540937.4</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>158472956130</v>
+        <v>158311406100</v>
       </c>
       <c r="E9" t="n">
         <v>1</v>
@@ -2193,10 +2193,10 @@
         <v>0</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>114969353.75</v>
+        <v>114798081.82</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>172454030625</v>
+        <v>172197122730</v>
       </c>
       <c r="E10" t="n">
         <v>4</v>
@@ -2218,10 +2218,10 @@
         <v>0</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>92671970.81999999</v>
+        <v>92527067.12</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>139007956230</v>
+        <v>138790600680</v>
       </c>
       <c r="E11" t="n">
         <v>3</v>
@@ -2318,16 +2318,16 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>2.887</v>
+        <v>2.862</v>
       </c>
       <c r="E2" s="6" t="n">
-        <v>12.058</v>
+        <v>11.951</v>
       </c>
       <c r="F2" t="n">
-        <v>0.856</v>
+        <v>0.8524</v>
       </c>
       <c r="G2" t="n">
-        <v>0.051</v>
+        <v>0.0515</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -2350,16 +2350,16 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>2.136</v>
+        <v>2.124</v>
       </c>
       <c r="E3" s="6" t="n">
-        <v>8.821999999999999</v>
+        <v>8.771000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8885999999999999</v>
+        <v>0.8871</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0387</v>
+        <v>0.0389</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -2382,13 +2382,13 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>2.315</v>
+        <v>2.308</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>9.587</v>
+        <v>9.555999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8529</v>
+        <v>0.8524</v>
       </c>
       <c r="G4" t="n">
         <v>0.0603</v>
@@ -2414,16 +2414,16 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>4.397</v>
+        <v>4.389</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>18.781</v>
+        <v>18.746</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7883</v>
+        <v>0.7877</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1528</v>
+        <v>0.1529</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -2446,16 +2446,16 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>9.124000000000001</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>41.8</v>
+        <v>41.78</v>
       </c>
       <c r="F6" t="n">
-        <v>0.885</v>
+        <v>0.8847</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2999</v>
+        <v>0.3001</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -3101,7 +3101,7 @@
         <v>276574.7</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>7216616.46</v>
+        <v>7170813.85</v>
       </c>
       <c r="G17" t="n">
         <v>31</v>
@@ -5605,16 +5605,16 @@
         </is>
       </c>
       <c r="E86" s="4" t="n">
-        <v>16888.75</v>
+        <v>17025.74</v>
       </c>
       <c r="F86" s="4" t="n">
-        <v>602295.47</v>
+        <v>604469.79</v>
       </c>
       <c r="G86" t="n">
         <v>31</v>
       </c>
       <c r="H86" s="6" t="n">
-        <v>6.94</v>
+        <v>7.06</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>

--- a/delivery130/03_Excel_Deliveries/9_Growth_Projection.xlsx
+++ b/delivery130/03_Excel_Deliveries/9_Growth_Projection.xlsx
@@ -605,16 +605,16 @@
         <v>1872809.25</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>13416173.56</v>
+        <v>13967970.3</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>12423050.36</v>
+        <v>13167510.89</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>14466833.65</v>
+        <v>14803865.6</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>20124260340</v>
+        <v>20951955450</v>
       </c>
       <c r="H2" s="5" t="n">
         <v>92</v>
@@ -637,19 +637,19 @@
         </is>
       </c>
       <c r="C3" s="4" t="n">
-        <v>2323531.26</v>
+        <v>2287660.09</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>15160578.02</v>
+        <v>15324463.18</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>14038326.45</v>
+        <v>14446267.54</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>16347847.56</v>
+        <v>16241536.07</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>22740867030</v>
+        <v>22986694770</v>
       </c>
       <c r="H3" s="5" t="n">
         <v>108</v>
@@ -672,19 +672,19 @@
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>3218095.33</v>
+        <v>3231443.55</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>14838831.44</v>
+        <v>15434186.74</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>13740396.95</v>
+        <v>14549703.19</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>16000904.06</v>
+        <v>16357825.9</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>22258247160</v>
+        <v>23151280110</v>
       </c>
       <c r="H4" s="5" t="n">
         <v>117</v>
@@ -707,19 +707,19 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>4262610.88</v>
+        <v>3966089.02</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>15174640.78</v>
+        <v>15352552.81</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>14051348.23</v>
+        <v>14472747.43</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>16363011.62</v>
+        <v>16271306.68</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>22761961170</v>
+        <v>23028829215</v>
       </c>
       <c r="H5" s="5" t="n">
         <v>118</v>
@@ -742,19 +742,19 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>3987687.25</v>
+        <v>4049998.77</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>14592925.06</v>
+        <v>15112250.71</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>13512693.62</v>
+        <v>14246216.28</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>15735740.03</v>
+        <v>16016624.01</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>21889387590</v>
+        <v>22668376065</v>
       </c>
       <c r="H6" s="5" t="n">
         <v>118</v>
@@ -777,19 +777,19 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>4568682.3</v>
+        <v>4358865.45</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>16490333.7</v>
+        <v>16579869.85</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>15269647.86</v>
+        <v>15629730.89</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>17781740.32</v>
+        <v>17572070.95</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>24735500550</v>
+        <v>24869804775</v>
       </c>
       <c r="H7" s="5" t="n">
         <v>118</v>
@@ -812,19 +812,19 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>5247262.71</v>
+        <v>5181762.78</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>16140366.27</v>
+        <v>16698582.16</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>14945586.54</v>
+        <v>15741640.18</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>17404365.92</v>
+        <v>17697887.44</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>24210549405</v>
+        <v>25047873240</v>
       </c>
       <c r="H8" s="5" t="n">
         <v>118</v>
@@ -847,19 +847,19 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>5450699.72</v>
+        <v>5431503.49</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>16505629.92</v>
+        <v>16610260.63</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>15283811.79</v>
+        <v>15658380.07</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>17798234.44</v>
+        <v>17604280.42</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>24758444880</v>
+        <v>24915390945</v>
       </c>
       <c r="H9" s="5" t="n">
         <v>119</v>
@@ -882,19 +882,19 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>5875940.25</v>
+        <v>5568133.79</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>15872891.1</v>
+        <v>16350272.56</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>14697911.03</v>
+        <v>15413291.09</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>17115943.97</v>
+        <v>17328733.7</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>23809336650</v>
+        <v>24525408840</v>
       </c>
       <c r="H10" s="5" t="n">
         <v>120</v>
@@ -917,19 +917,19 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>6943009.98</v>
+        <v>6768002.84</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>17936724.12</v>
+        <v>17938121.62</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>16608970.2</v>
+        <v>16910145.62</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>19341401.84</v>
+        <v>19011605.55</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>26905086180</v>
+        <v>26907182430</v>
       </c>
       <c r="H11" s="5" t="n">
         <v>120</v>
@@ -952,19 +952,19 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>8947657.449999999</v>
+        <v>7959432.59</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>17556060.56</v>
+        <v>18066559.04</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>16256485.01</v>
+        <v>17031222.71</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>18930927.4</v>
+        <v>19147729.15</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>26334090840</v>
+        <v>27099838560</v>
       </c>
       <c r="H12" s="5" t="n">
         <v>120</v>
@@ -987,19 +987,19 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>12461484.25</v>
+        <v>12244513.48</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>17953362</v>
+        <v>17971002.06</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>16624376.48</v>
+        <v>16941141.79</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>19359342.68</v>
+        <v>19046453.68</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>26930043000</v>
+        <v>26956503090</v>
       </c>
       <c r="H13" s="5" t="n">
         <v>121</v>
@@ -1022,19 +1022,19 @@
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>12548977.87</v>
+        <v>12174306.36</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>17265124.76</v>
+        <v>17689715.32</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>15987085.53</v>
+        <v>16675974.69</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>18617207.56</v>
+        <v>18748333.7</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>25897687140</v>
+        <v>26534572980</v>
       </c>
       <c r="H14" s="5" t="n">
         <v>122</v>
@@ -1057,19 +1057,19 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>13725219.23</v>
+        <v>13250288.4</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>19509979.48</v>
+        <v>19407643.73</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>18065766.4</v>
+        <v>18295454.16</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>21037863.47</v>
+        <v>20569069.34</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>29264969220</v>
+        <v>29111465595</v>
       </c>
       <c r="H15" s="5" t="n">
         <v>122</v>
@@ -1092,22 +1092,22 @@
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>16545833.22</v>
+        <v>15980760.5</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>19095927.39</v>
+        <v>19546602.97</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>17682364.23</v>
+        <v>18426450.09</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>20591385.73</v>
+        <v>20716344.41</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>28643891085</v>
+        <v>29319904455</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1127,19 +1127,19 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>17741891.5</v>
+        <v>17198484.51</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>19528076.7</v>
+        <v>19443217.79</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>18082523.98</v>
+        <v>18328989.58</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>21057377.93</v>
+        <v>20606772.28</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>29292115050</v>
+        <v>29164826685</v>
       </c>
       <c r="H17" s="5" t="n">
         <v>127</v>
@@ -1162,19 +1162,19 @@
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>19660327.06</v>
+        <v>19163324.49</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>18779473.2</v>
+        <v>19138887.56</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>17389335.35</v>
+        <v>18042099.53</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>20250149.08</v>
+        <v>20284229.79</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>28169209800</v>
+        <v>28708331340</v>
       </c>
       <c r="H18" s="5" t="n">
         <v>127</v>
@@ -1197,19 +1197,19 @@
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>23324978.41</v>
+        <v>22322937.87</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>21221227.29</v>
+        <v>20997551.65</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>19650340.25</v>
+        <v>19794249.57</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>22883124.14</v>
+        <v>22254123.26</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>31831840935</v>
+        <v>31496327475</v>
       </c>
       <c r="H19" s="5" t="n">
         <v>127</v>
@@ -1232,19 +1232,19 @@
         </is>
       </c>
       <c r="C20" s="4" t="n">
-        <v>20941938.6</v>
+        <v>21271911.06</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>20770858.1</v>
+        <v>21147894.67</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>19233309.33</v>
+        <v>19935976.92</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>22397485.21</v>
+        <v>22413463.37</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>31156287150</v>
+        <v>31721842005</v>
       </c>
       <c r="H20" s="5" t="n">
         <v>127</v>
@@ -1267,19 +1267,19 @@
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>21429816.51</v>
+        <v>21057326.34</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>21240911.84</v>
+        <v>21036040</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>19668567.66</v>
+        <v>19830532.28</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>22904350.24</v>
+        <v>22294914.9</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>31861367760</v>
+        <v>31554060000</v>
       </c>
       <c r="H21" s="5" t="n">
         <v>127</v>
@@ -1302,19 +1302,19 @@
         </is>
       </c>
       <c r="C22" s="4" t="n">
-        <v>20850286.58</v>
+        <v>21085056.69</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>20426647.27</v>
+        <v>20706778.5</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>18914578.47</v>
+        <v>19520139.7</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>22026318.21</v>
+        <v>21945949.17</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>30639970905</v>
+        <v>31060167750</v>
       </c>
       <c r="H22" s="5" t="n">
         <v>127</v>
@@ -1337,19 +1337,19 @@
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>23032147.91</v>
+        <v>22607539.11</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>23082571.06</v>
+        <v>22717707.59</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>21373899.3</v>
+        <v>21415828.91</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>24890235.23</v>
+        <v>24077219.73</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>34623856590</v>
+        <v>34076561385</v>
       </c>
       <c r="H23" s="5" t="n">
         <v>127</v>
@@ -1372,19 +1372,19 @@
         </is>
       </c>
       <c r="C24" s="4" t="n">
-        <v>23051208.35</v>
+        <v>23468243.91</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>22592699.36</v>
+        <v>22880366.98</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>20920290.01</v>
+        <v>21569166.81</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>24362000.22</v>
+        <v>24249613.26</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>33889049040</v>
+        <v>34320550470</v>
       </c>
       <c r="H24" s="5" t="n">
         <v>127</v>
@@ -1407,19 +1407,19 @@
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>23154211.86</v>
+        <v>22756191.69</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>23103982.17</v>
+        <v>22759348.98</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>21393725.46</v>
+        <v>21455083.96</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>24913323.1</v>
+        <v>24121353.09</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>34655973255</v>
+        <v>34139023470</v>
       </c>
       <c r="H25" s="5" t="n">
         <v>128</v>
@@ -1442,19 +1442,19 @@
         </is>
       </c>
       <c r="C26" s="4" t="n">
-        <v>20985647.25</v>
+        <v>21542153.27</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>22218297.31</v>
+        <v>22403113.8</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>20573602.82</v>
+        <v>21119263.48</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>23958277.64</v>
+        <v>23743799.48</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>33327445965</v>
+        <v>33604670700</v>
       </c>
       <c r="H26" s="5" t="n">
         <v>129</v>
@@ -1477,19 +1477,19 @@
         </is>
       </c>
       <c r="C27" s="4" t="n">
-        <v>24001481.19</v>
+        <v>23814216.41</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>25107175.92</v>
+        <v>24578781.7</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>23248634.14</v>
+        <v>23170250.86</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>27073392.86</v>
+        <v>26049667.44</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>37660763880</v>
+        <v>36868172550</v>
       </c>
       <c r="H27" s="5" t="n">
         <v>129</v>
@@ -1512,19 +1512,19 @@
         </is>
       </c>
       <c r="C28" s="4" t="n">
-        <v>23834738.27</v>
+        <v>23961840.73</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>24574336.88</v>
+        <v>24754766.42</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>22755238.15</v>
+        <v>23336150.46</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>26498825.61</v>
+        <v>26236183.74</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>36861505320</v>
+        <v>37132149630</v>
       </c>
       <c r="H28" s="5" t="n">
         <v>129</v>
@@ -1547,19 +1547,19 @@
         </is>
       </c>
       <c r="C29" s="4" t="n">
-        <v>24798685.61</v>
+        <v>24569426.28</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>25130465.02</v>
+        <v>24623834.42</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>23270199.29</v>
+        <v>23212721.75</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>27098505.8</v>
+        <v>26097416.28</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>37695697530</v>
+        <v>36935751630</v>
       </c>
       <c r="H29" s="5" t="n">
         <v>128</v>
@@ -1582,19 +1582,19 @@
         </is>
       </c>
       <c r="C30" s="4" t="n">
-        <v>25010047.72</v>
+        <v>24721771.73</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>24167095.5</v>
+        <v>24238415.84</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>22378142.54</v>
+        <v>22849390.27</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>26059691.96</v>
+        <v>25688932.82</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>36250643250</v>
+        <v>36357623760</v>
       </c>
       <c r="H30" s="5" t="n">
         <v>128</v>
@@ -1617,19 +1617,19 @@
         </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>28565228.86</v>
+        <v>27542908.02</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>27309361.73</v>
+        <v>26592318.23</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>25287804.63</v>
+        <v>25068398.09</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>29448038.32</v>
+        <v>28183701.49</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>40964042595</v>
+        <v>39888477345</v>
       </c>
       <c r="H31" s="5" t="n">
         <v>127</v>
@@ -1652,19 +1652,19 @@
         </is>
       </c>
       <c r="C32" s="4" t="n">
-        <v>28556269.52</v>
+        <v>28424707.67</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>26729786.62</v>
+        <v>26782719.93</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>24751132.18</v>
+        <v>25247888.48</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>28823074.97</v>
+        <v>28385497.53</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>40094679930</v>
+        <v>40174079895</v>
       </c>
       <c r="H32" s="5" t="n">
         <v>127</v>
@@ -1688,16 +1688,16 @@
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" s="4" t="n">
-        <v>27334693.55</v>
+        <v>26641061.75</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>25311261.28</v>
+        <v>25114348.27</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>29475353.95</v>
+        <v>28235361.99</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>41002040325</v>
+        <v>39961592625</v>
       </c>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
@@ -1719,16 +1719,16 @@
       </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" s="4" t="n">
-        <v>26286825.52</v>
+        <v>26224069.01</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>24340960.98</v>
+        <v>24721252.05</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>28345424.29</v>
+        <v>27793414.86</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>39430238280</v>
+        <v>39336103515</v>
       </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
@@ -1750,16 +1750,16 @@
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" s="4" t="n">
-        <v>29704704.35</v>
+        <v>28770807.18</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>27505833.63</v>
+        <v>27122044.85</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>32030967.28</v>
+        <v>30492559.32</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>44557056525</v>
+        <v>43156210770</v>
       </c>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
@@ -1781,16 +1781,16 @@
       </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" s="4" t="n">
-        <v>29074293.89</v>
+        <v>28976806.92</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>26922088.88</v>
+        <v>27316239.41</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>31351187.52</v>
+        <v>30710886.85</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>43611440835</v>
+        <v>43465210380</v>
       </c>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
@@ -1812,16 +1812,16 @@
       </c>
       <c r="C37" t="inlineStr"/>
       <c r="D37" s="4" t="n">
-        <v>29732258.06</v>
+        <v>28823543.85</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>27531347.7</v>
+        <v>27171759.35</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>32060678.81</v>
+        <v>30548451.94</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>44598387090</v>
+        <v>43235315775</v>
       </c>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
@@ -1843,16 +1843,16 @@
       </c>
       <c r="C38" t="inlineStr"/>
       <c r="D38" s="4" t="n">
-        <v>28592480.05</v>
+        <v>28372390.34</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>26475940.99</v>
+        <v>26746460</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>30831641.42</v>
+        <v>30070299.73</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>42888720075</v>
+        <v>42558585510</v>
       </c>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
@@ -1874,16 +1874,16 @@
       </c>
       <c r="C39" t="inlineStr"/>
       <c r="D39" s="4" t="n">
-        <v>32310145.86</v>
+        <v>31127761.73</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>29918409.09</v>
+        <v>29343929.92</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>34840448.59</v>
+        <v>32990562.8</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>48465218790</v>
+        <v>46691642595</v>
       </c>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
@@ -1905,16 +1905,16 @@
       </c>
       <c r="C40" t="inlineStr"/>
       <c r="D40" s="4" t="n">
-        <v>31624441.21</v>
+        <v>31350637.32</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>29283463.26</v>
+        <v>29554033.23</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>34101044.39</v>
+        <v>33226776.09</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>47436661815</v>
+        <v>47025955980</v>
       </c>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
@@ -1990,13 +1990,13 @@
         <v>2019</v>
       </c>
       <c r="B2" s="4" t="n">
-        <v>11677046.72</v>
+        <v>11358001.91</v>
       </c>
       <c r="C2" s="4" t="n">
-        <v>58590223.8</v>
+        <v>60079173.03</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>87885335700</v>
+        <v>90118759545</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -2015,13 +2015,13 @@
         <v>2020</v>
       </c>
       <c r="B3" s="4" t="n">
-        <v>19254331.98</v>
+        <v>19022130.49</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>63729254.95</v>
+        <v>65000963.35</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>95593882425</v>
+        <v>97501445025</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -2040,13 +2040,13 @@
         <v>2021</v>
       </c>
       <c r="B4" s="4" t="n">
-        <v>34228091.93</v>
+        <v>32540082.7</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>69319037.78</v>
+        <v>70325955.28</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>103978556670</v>
+        <v>105488932920</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -2065,13 +2065,13 @@
         <v>2022</v>
       </c>
       <c r="B5" s="4" t="n">
-        <v>60561921.82</v>
+        <v>58603839.77</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>75399108.33</v>
+        <v>76087179.81</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>113098662495</v>
+        <v>114130769715</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -2090,13 +2090,13 @@
         <v>2023</v>
       </c>
       <c r="B6" s="4" t="n">
-        <v>85357060.58</v>
+        <v>83815499.76000001</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>82012470.43000001</v>
+        <v>82320373.88</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>123018705645</v>
+        <v>123480560820</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -2115,13 +2115,13 @@
         <v>2024</v>
       </c>
       <c r="B7" s="4" t="n">
-        <v>90087854.7</v>
+        <v>89917031.40000001</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>89205899.86</v>
+        <v>89064202.05</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>133808849790</v>
+        <v>133596303075</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -2140,13 +2140,13 @@
         <v>2025</v>
       </c>
       <c r="B8" s="4" t="n">
-        <v>93620552.31999999</v>
+        <v>93887636.69</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>97030275.13</v>
+        <v>96360496.34</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>145545412695</v>
+        <v>144540744510</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -2165,13 +2165,13 @@
         <v>2026</v>
       </c>
       <c r="B9" s="4" t="n">
-        <v>82131546.09999999</v>
+        <v>80689387.42</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>105540937.4</v>
+        <v>104254515.75</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>158311406100</v>
+        <v>156381773625</v>
       </c>
       <c r="E9" t="n">
         <v>1</v>
@@ -2193,10 +2193,10 @@
         <v>0</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>114798081.82</v>
+        <v>112795226.96</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>172197122730</v>
+        <v>169192840440</v>
       </c>
       <c r="E10" t="n">
         <v>4</v>
@@ -2218,10 +2218,10 @@
         <v>0</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>92527067.12</v>
+        <v>90850789.39</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>138790600680</v>
+        <v>136276184085</v>
       </c>
       <c r="E11" t="n">
         <v>3</v>
@@ -2318,16 +2318,16 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>2.862</v>
+        <v>2.407</v>
       </c>
       <c r="E2" s="6" t="n">
-        <v>11.951</v>
+        <v>9.983000000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8524</v>
+        <v>0.8561</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0515</v>
+        <v>0.0412</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -2350,16 +2350,16 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>2.124</v>
+        <v>1.988</v>
       </c>
       <c r="E3" s="6" t="n">
-        <v>8.771000000000001</v>
+        <v>8.192</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8871</v>
+        <v>0.9121</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0389</v>
+        <v>0.0299</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -2382,16 +2382,16 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>2.308</v>
+        <v>2.486</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>9.555999999999999</v>
+        <v>10.321</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8524</v>
+        <v>0.8479</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0603</v>
+        <v>0.0625</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -2414,16 +2414,16 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>4.389</v>
+        <v>4.683</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>18.746</v>
+        <v>20.091</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7877</v>
+        <v>0.7736</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1529</v>
+        <v>0.1684</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -2446,16 +2446,16 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>9.119999999999999</v>
+        <v>9.212999999999999</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>41.78</v>
+        <v>42.262</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8847</v>
+        <v>0.891</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3001</v>
+        <v>0.2933</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -2557,16 +2557,16 @@
         </is>
       </c>
       <c r="E2" s="4" t="n">
-        <v>3036780.74</v>
+        <v>2382125.7</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>42960525.69</v>
+        <v>42132573.33</v>
       </c>
       <c r="G2" t="n">
         <v>31</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>46.97</v>
+        <v>42.13</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -2594,16 +2594,16 @@
         </is>
       </c>
       <c r="E3" s="4" t="n">
-        <v>2022343.04</v>
+        <v>1917521.68</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>37196147.9</v>
+        <v>36690962.97</v>
       </c>
       <c r="G3" t="n">
         <v>31</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>100.5</v>
+        <v>99.03</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -2631,10 +2631,10 @@
         </is>
       </c>
       <c r="E4" s="4" t="n">
-        <v>2542924.08</v>
+        <v>2697142.39</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>25547585.53</v>
+        <v>24678101.56</v>
       </c>
       <c r="G4" t="n">
         <v>30</v>
@@ -2666,16 +2666,16 @@
         </is>
       </c>
       <c r="E5" s="4" t="n">
-        <v>1287564.19</v>
+        <v>1304093.05</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>24381708.74</v>
+        <v>24046358.57</v>
       </c>
       <c r="G5" t="n">
         <v>31</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>26.95</v>
+        <v>27.18</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -2703,16 +2703,16 @@
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>787978.34</v>
+        <v>779739.88</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>22213149.57</v>
+        <v>22084859.63</v>
       </c>
       <c r="G6" t="n">
         <v>31</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>252.42</v>
+        <v>251.91</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -2740,10 +2740,10 @@
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>1382238.77</v>
+        <v>1288433.78</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>21212971.67</v>
+        <v>21064373.04</v>
       </c>
       <c r="G7" t="n">
         <v>23</v>
@@ -2775,10 +2775,10 @@
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>988820.34</v>
+        <v>936666.34</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>18832180.03</v>
+        <v>18611803.06</v>
       </c>
       <c r="G8" t="n">
         <v>30</v>
@@ -2810,10 +2810,10 @@
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>1079009.1</v>
+        <v>1117981.34</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>15352902.44</v>
+        <v>14976897.99</v>
       </c>
       <c r="G9" t="n">
         <v>28</v>
@@ -2845,16 +2845,16 @@
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>699292.23</v>
+        <v>681751.15</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>14554700.57</v>
+        <v>14397031.45</v>
       </c>
       <c r="G10" t="n">
         <v>31</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>96.7</v>
+        <v>96.01000000000001</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -2882,16 +2882,16 @@
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>447818.47</v>
+        <v>444346.68</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>10816064.96</v>
+        <v>10710505.7</v>
       </c>
       <c r="G11" t="n">
         <v>31</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>62.6</v>
+        <v>62.42</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -2919,10 +2919,10 @@
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>947262.58</v>
+        <v>955063.2</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>10729833.23</v>
+        <v>10580075.97</v>
       </c>
       <c r="G12" t="n">
         <v>29</v>
@@ -2954,10 +2954,10 @@
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>437255.96</v>
+        <v>417485.58</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>10347004.44</v>
+        <v>10155723.65</v>
       </c>
       <c r="G13" t="n">
         <v>29</v>
@@ -2989,16 +2989,16 @@
         </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>280354.33</v>
+        <v>294603.92</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>10114272.21</v>
+        <v>10065292.11</v>
       </c>
       <c r="G14" t="n">
         <v>31</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>4.92</v>
+        <v>5.64</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -3026,16 +3026,16 @@
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>367371.14</v>
+        <v>366592.92</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>8484168.189999999</v>
+        <v>8510021.140000001</v>
       </c>
       <c r="G15" t="n">
         <v>31</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>101.4</v>
+        <v>101.34</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -3063,10 +3063,10 @@
         </is>
       </c>
       <c r="E16" s="4" t="n">
-        <v>460075.44</v>
+        <v>451309.32</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>7410299.57</v>
+        <v>7352934.24</v>
       </c>
       <c r="G16" t="n">
         <v>29</v>
@@ -3098,16 +3098,16 @@
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>276574.7</v>
+        <v>278114.23</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>7170813.85</v>
+        <v>7131291.98</v>
       </c>
       <c r="G17" t="n">
         <v>31</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>6.91</v>
+        <v>6.99</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -3135,16 +3135,16 @@
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>331953.81</v>
+        <v>327684.7</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>6823995.89</v>
+        <v>6696036.78</v>
       </c>
       <c r="G18" t="n">
         <v>31</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>161.89</v>
+        <v>161.42</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -3172,10 +3172,10 @@
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>510451.71</v>
+        <v>505950.6</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>6746466.3</v>
+        <v>6631128.34</v>
       </c>
       <c r="G19" t="n">
         <v>24</v>
@@ -3207,16 +3207,16 @@
         </is>
       </c>
       <c r="E20" s="4" t="n">
-        <v>367389.92</v>
+        <v>373037.68</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>6528915.81</v>
+        <v>6432234.98</v>
       </c>
       <c r="G20" t="n">
         <v>31</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>36.77</v>
+        <v>37.06</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -3244,10 +3244,10 @@
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>453303.98</v>
+        <v>449356.4</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>6424843.63</v>
+        <v>6322014.52</v>
       </c>
       <c r="G21" t="n">
         <v>30</v>
@@ -3279,16 +3279,16 @@
         </is>
       </c>
       <c r="E22" s="4" t="n">
-        <v>368019.87</v>
+        <v>358613.91</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>6321973.44</v>
+        <v>6264449.94</v>
       </c>
       <c r="G22" t="n">
         <v>31</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>100.53</v>
+        <v>99.81</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Tiwa Savage</t>
+          <t>Darkoo</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3308,7 +3308,7 @@
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>38197.68</v>
+        <v>0</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3316,27 +3316,25 @@
         </is>
       </c>
       <c r="E23" s="4" t="n">
-        <v>234075.1</v>
+        <v>215115.91</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>5779856.56</v>
+        <v>5677837.49</v>
       </c>
       <c r="G23" t="n">
-        <v>31</v>
-      </c>
-      <c r="H23" s="6" t="n">
-        <v>28.41</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
-          <t>OBS</t>
+          <t>UNK</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Darkoo</t>
+          <t>Tiwa Savage</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3345,7 +3343,7 @@
         </is>
       </c>
       <c r="C24" s="4" t="n">
-        <v>0</v>
+        <v>38197.68</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3353,18 +3351,20 @@
         </is>
       </c>
       <c r="E24" s="4" t="n">
-        <v>216785.36</v>
+        <v>214411.61</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>5778059.73</v>
+        <v>5634666.2</v>
       </c>
       <c r="G24" t="n">
-        <v>30</v>
-      </c>
-      <c r="H24" t="inlineStr"/>
+        <v>31</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>26.86</v>
+      </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>UNK</t>
+          <t>OBS</t>
         </is>
       </c>
     </row>
@@ -3388,10 +3388,10 @@
         </is>
       </c>
       <c r="E25" s="4" t="n">
-        <v>324983.97</v>
+        <v>297960.82</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>5473960.12</v>
+        <v>5390486.99</v>
       </c>
       <c r="G25" t="n">
         <v>30</v>
@@ -3423,16 +3423,16 @@
         </is>
       </c>
       <c r="E26" s="4" t="n">
-        <v>230676.89</v>
+        <v>226215.23</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>5279335.24</v>
+        <v>5228815.89</v>
       </c>
       <c r="G26" t="n">
         <v>31</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>31.85</v>
+        <v>31.5</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -3460,16 +3460,16 @@
         </is>
       </c>
       <c r="E27" s="4" t="n">
-        <v>379467.96</v>
+        <v>366418.63</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>4919045.49</v>
+        <v>4871954.15</v>
       </c>
       <c r="G27" t="n">
         <v>31</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>30.06</v>
+        <v>29.43</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -3497,16 +3497,16 @@
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>209714.46</v>
+        <v>200710.49</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>4453253.37</v>
+        <v>4401723.56</v>
       </c>
       <c r="G28" t="n">
         <v>31</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>18.2</v>
+        <v>17.49</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -3534,16 +3534,16 @@
         </is>
       </c>
       <c r="E29" s="4" t="n">
-        <v>354620.42</v>
+        <v>342646.77</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>4414442.96</v>
+        <v>4256313.57</v>
       </c>
       <c r="G29" t="n">
         <v>31</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>71.62</v>
+        <v>70.81</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -3571,16 +3571,16 @@
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>264709.98</v>
+        <v>269444.04</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>4165320.28</v>
+        <v>4136526.5</v>
       </c>
       <c r="G30" t="n">
         <v>31</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>61.68</v>
+        <v>62.08</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -3608,16 +3608,16 @@
         </is>
       </c>
       <c r="E31" s="4" t="n">
-        <v>131504.36</v>
+        <v>131783.18</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>4162272.23</v>
+        <v>4134620.21</v>
       </c>
       <c r="G31" t="n">
         <v>31</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>13.39</v>
+        <v>13.43</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -3645,10 +3645,10 @@
         </is>
       </c>
       <c r="E32" s="4" t="n">
-        <v>172459.18</v>
+        <v>164444.61</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>3833710.35</v>
+        <v>3788538.52</v>
       </c>
       <c r="G32" t="n">
         <v>30</v>
@@ -3680,10 +3680,10 @@
         </is>
       </c>
       <c r="E33" s="4" t="n">
-        <v>339446.26</v>
+        <v>347814</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>3640825.04</v>
+        <v>3561767.71</v>
       </c>
       <c r="G33" t="n">
         <v>16</v>
@@ -3715,10 +3715,10 @@
         </is>
       </c>
       <c r="E34" s="4" t="n">
-        <v>329129.97</v>
+        <v>323493.73</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>3485209.79</v>
+        <v>3357545.17</v>
       </c>
       <c r="G34" t="n">
         <v>30</v>
@@ -3750,10 +3750,10 @@
         </is>
       </c>
       <c r="E35" s="4" t="n">
-        <v>216702.9</v>
+        <v>222049.17</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>3384166.51</v>
+        <v>3342993.89</v>
       </c>
       <c r="G35" t="n">
         <v>30</v>
@@ -3785,16 +3785,16 @@
         </is>
       </c>
       <c r="E36" s="4" t="n">
-        <v>78868.97</v>
+        <v>79227.89</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>3327631.87</v>
+        <v>3305295.78</v>
       </c>
       <c r="G36" t="n">
         <v>31</v>
       </c>
       <c r="H36" s="6" t="n">
-        <v>-3.38</v>
+        <v>-3.32</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -3822,16 +3822,16 @@
         </is>
       </c>
       <c r="E37" s="4" t="n">
-        <v>186639.68</v>
+        <v>171415.38</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>3178110.88</v>
+        <v>3093813.08</v>
       </c>
       <c r="G37" t="n">
         <v>31</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>32.66</v>
+        <v>31.11</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -3859,10 +3859,10 @@
         </is>
       </c>
       <c r="E38" s="4" t="n">
-        <v>310797.54</v>
+        <v>299130.13</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>3161788.41</v>
+        <v>3085875.27</v>
       </c>
       <c r="G38" t="n">
         <v>29</v>
@@ -3894,16 +3894,16 @@
         </is>
       </c>
       <c r="E39" s="4" t="n">
-        <v>157650.13</v>
+        <v>148153.78</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>3049494.19</v>
+        <v>3002662.45</v>
       </c>
       <c r="G39" t="n">
         <v>31</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>55.39</v>
+        <v>54.06</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -3931,16 +3931,16 @@
         </is>
       </c>
       <c r="E40" s="4" t="n">
-        <v>109171.56</v>
+        <v>106539.79</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>3018136.96</v>
+        <v>2989080.97</v>
       </c>
       <c r="G40" t="n">
         <v>31</v>
       </c>
       <c r="H40" s="6" t="n">
-        <v>6.08</v>
+        <v>5.72</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -3951,7 +3951,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Seyi Vibez</t>
+          <t>Tempoe</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3968,13 +3968,13 @@
         </is>
       </c>
       <c r="E41" s="4" t="n">
-        <v>198428.15</v>
+        <v>219048.12</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>2763054.1</v>
+        <v>2811305.3</v>
       </c>
       <c r="G41" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
@@ -3986,7 +3986,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Tempoe</t>
+          <t>Seyi Vibez</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4003,13 +4003,13 @@
         </is>
       </c>
       <c r="E42" s="4" t="n">
-        <v>215903.39</v>
+        <v>197534.9</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>2760230.11</v>
+        <v>2665631.25</v>
       </c>
       <c r="G42" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
@@ -4038,16 +4038,16 @@
         </is>
       </c>
       <c r="E43" s="4" t="n">
-        <v>122036.36</v>
+        <v>123514</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>2472020.95</v>
+        <v>2438650.91</v>
       </c>
       <c r="G43" t="n">
         <v>31</v>
       </c>
       <c r="H43" s="6" t="n">
-        <v>36.55</v>
+        <v>36.77</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -4075,16 +4075,16 @@
         </is>
       </c>
       <c r="E44" s="4" t="n">
-        <v>194467.17</v>
+        <v>198453.67</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>2402569.34</v>
+        <v>2354581.17</v>
       </c>
       <c r="G44" t="n">
         <v>31</v>
       </c>
       <c r="H44" s="6" t="n">
-        <v>218.6</v>
+        <v>219.5</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -4112,10 +4112,10 @@
         </is>
       </c>
       <c r="E45" s="4" t="n">
-        <v>248105.42</v>
+        <v>238889</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>2331977.97</v>
+        <v>2276325.81</v>
       </c>
       <c r="G45" t="n">
         <v>19</v>
@@ -4130,7 +4130,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Mayorkun</t>
+          <t>Spyro</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4139,7 +4139,7 @@
         </is>
       </c>
       <c r="C46" s="4" t="n">
-        <v>12473.45</v>
+        <v>0</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4147,27 +4147,25 @@
         </is>
       </c>
       <c r="E46" s="4" t="n">
-        <v>97782.52</v>
+        <v>124313.86</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>2263306.38</v>
+        <v>2218620.65</v>
       </c>
       <c r="G46" t="n">
-        <v>31</v>
-      </c>
-      <c r="H46" s="6" t="n">
-        <v>32.85</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
-          <t>OBS</t>
+          <t>UNK</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Spyro</t>
+          <t>Mayorkun</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4176,7 +4174,7 @@
         </is>
       </c>
       <c r="C47" s="4" t="n">
-        <v>0</v>
+        <v>12473.45</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4184,18 +4182,20 @@
         </is>
       </c>
       <c r="E47" s="4" t="n">
-        <v>125916.62</v>
+        <v>87978.53</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>2232607.09</v>
+        <v>2180207.93</v>
       </c>
       <c r="G47" t="n">
-        <v>30</v>
-      </c>
-      <c r="H47" t="inlineStr"/>
+        <v>31</v>
+      </c>
+      <c r="H47" s="6" t="n">
+        <v>30.92</v>
+      </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>UNK</t>
+          <t>OBS</t>
         </is>
       </c>
     </row>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="E48" s="4" t="n">
-        <v>133398.27</v>
+        <v>133241.55</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>2221868.05</v>
+        <v>2166472.02</v>
       </c>
       <c r="G48" t="n">
         <v>29</v>
@@ -4254,16 +4254,16 @@
         </is>
       </c>
       <c r="E49" s="4" t="n">
-        <v>117358.62</v>
+        <v>118429.23</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>2181993.44</v>
+        <v>2159789.79</v>
       </c>
       <c r="G49" t="n">
         <v>31</v>
       </c>
       <c r="H49" s="6" t="n">
-        <v>53.19</v>
+        <v>53.38</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -4291,16 +4291,16 @@
         </is>
       </c>
       <c r="E50" s="4" t="n">
-        <v>87229.87</v>
+        <v>87679.61</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>2124191.42</v>
+        <v>2116193.62</v>
       </c>
       <c r="G50" t="n">
         <v>31</v>
       </c>
       <c r="H50" s="6" t="n">
-        <v>12.13</v>
+        <v>12.21</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -4328,10 +4328,10 @@
         </is>
       </c>
       <c r="E51" s="4" t="n">
-        <v>203561.07</v>
+        <v>166337.68</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>2123841.93</v>
+        <v>2115995.57</v>
       </c>
       <c r="G51" t="n">
         <v>17</v>
@@ -4363,10 +4363,10 @@
         </is>
       </c>
       <c r="E52" s="4" t="n">
-        <v>171589.35</v>
+        <v>174628.86</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>2105596.52</v>
+        <v>2073910.31</v>
       </c>
       <c r="G52" t="n">
         <v>29</v>
@@ -4398,16 +4398,16 @@
         </is>
       </c>
       <c r="E53" s="4" t="n">
-        <v>84591.58</v>
+        <v>85467.75999999999</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>1985119.62</v>
+        <v>1963392.14</v>
       </c>
       <c r="G53" t="n">
         <v>31</v>
       </c>
       <c r="H53" s="6" t="n">
-        <v>18.83</v>
+        <v>19</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -4435,16 +4435,16 @@
         </is>
       </c>
       <c r="E54" s="4" t="n">
-        <v>169994.38</v>
+        <v>167165.72</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>1921433.21</v>
+        <v>1874469.21</v>
       </c>
       <c r="G54" t="n">
         <v>31</v>
       </c>
       <c r="H54" s="6" t="n">
-        <v>45.81</v>
+        <v>45.48</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -4472,16 +4472,16 @@
         </is>
       </c>
       <c r="E55" s="4" t="n">
-        <v>136765.06</v>
+        <v>140130.18</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>1893076.44</v>
+        <v>1871955.68</v>
       </c>
       <c r="G55" t="n">
         <v>31</v>
       </c>
       <c r="H55" s="6" t="n">
-        <v>29.35</v>
+        <v>29.79</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -4509,16 +4509,16 @@
         </is>
       </c>
       <c r="E56" s="4" t="n">
-        <v>205774.52</v>
+        <v>170922.77</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>1815324.43</v>
+        <v>1776846.14</v>
       </c>
       <c r="G56" t="n">
         <v>31</v>
       </c>
       <c r="H56" s="6" t="n">
-        <v>128.17</v>
+        <v>122.4</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -4546,10 +4546,10 @@
         </is>
       </c>
       <c r="E57" s="4" t="n">
-        <v>161459.17</v>
+        <v>163643.08</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>1706616.12</v>
+        <v>1697868.35</v>
       </c>
       <c r="G57" t="n">
         <v>16</v>
@@ -4581,16 +4581,16 @@
         </is>
       </c>
       <c r="E58" s="4" t="n">
-        <v>53155.51</v>
+        <v>53091.51</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>1703342.17</v>
+        <v>1687892.37</v>
       </c>
       <c r="G58" t="n">
         <v>31</v>
       </c>
       <c r="H58" s="6" t="n">
-        <v>94.33</v>
+        <v>94.3</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -4618,16 +4618,16 @@
         </is>
       </c>
       <c r="E59" s="4" t="n">
-        <v>69357.25</v>
+        <v>68622.53</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>1682344.38</v>
+        <v>1679899.47</v>
       </c>
       <c r="G59" t="n">
         <v>31</v>
       </c>
       <c r="H59" s="6" t="n">
-        <v>41.09</v>
+        <v>40.88</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -4655,16 +4655,16 @@
         </is>
       </c>
       <c r="E60" s="4" t="n">
-        <v>164486.45</v>
+        <v>140406.59</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>1640887.28</v>
+        <v>1594243.47</v>
       </c>
       <c r="G60" t="n">
         <v>31</v>
       </c>
       <c r="H60" s="6" t="n">
-        <v>656.42</v>
+        <v>640.08</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -4692,16 +4692,16 @@
         </is>
       </c>
       <c r="E61" s="4" t="n">
-        <v>82301.45</v>
+        <v>80464.38</v>
       </c>
       <c r="F61" s="4" t="n">
-        <v>1601003.86</v>
+        <v>1570501.27</v>
       </c>
       <c r="G61" t="n">
         <v>31</v>
       </c>
       <c r="H61" s="6" t="n">
-        <v>32.13</v>
+        <v>31.72</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -4729,16 +4729,16 @@
         </is>
       </c>
       <c r="E62" s="4" t="n">
-        <v>48558.85</v>
+        <v>50419.39</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>1571391.77</v>
+        <v>1556865.67</v>
       </c>
       <c r="G62" t="n">
         <v>31</v>
       </c>
       <c r="H62" s="6" t="n">
-        <v>7.99</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -4766,16 +4766,16 @@
         </is>
       </c>
       <c r="E63" s="4" t="n">
-        <v>199221.33</v>
+        <v>200814.19</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>1535144.65</v>
+        <v>1541571.13</v>
       </c>
       <c r="G63" t="n">
         <v>31</v>
       </c>
       <c r="H63" s="6" t="n">
-        <v>63.28</v>
+        <v>63.46</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -4803,10 +4803,10 @@
         </is>
       </c>
       <c r="E64" s="4" t="n">
-        <v>93931.03</v>
+        <v>94464.25</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>1527362.74</v>
+        <v>1481192.61</v>
       </c>
       <c r="G64" t="n">
         <v>30</v>
@@ -4838,16 +4838,16 @@
         </is>
       </c>
       <c r="E65" s="4" t="n">
-        <v>57851.22</v>
+        <v>61025.87</v>
       </c>
       <c r="F65" s="4" t="n">
-        <v>1488874.05</v>
+        <v>1463004.62</v>
       </c>
       <c r="G65" t="n">
         <v>31</v>
       </c>
       <c r="H65" s="6" t="n">
-        <v>5.32</v>
+        <v>6.1</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -4875,16 +4875,16 @@
         </is>
       </c>
       <c r="E66" s="4" t="n">
-        <v>87422.21000000001</v>
+        <v>84628.27</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>1414035.25</v>
+        <v>1392259.73</v>
       </c>
       <c r="G66" t="n">
         <v>31</v>
       </c>
       <c r="H66" s="6" t="n">
-        <v>18.72</v>
+        <v>18.19</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
@@ -4912,16 +4912,16 @@
         </is>
       </c>
       <c r="E67" s="4" t="n">
-        <v>73981.37</v>
+        <v>78271.47</v>
       </c>
       <c r="F67" s="4" t="n">
-        <v>1409442.47</v>
+        <v>1387890.35</v>
       </c>
       <c r="G67" t="n">
         <v>31</v>
       </c>
       <c r="H67" s="6" t="n">
-        <v>29.48</v>
+        <v>30.49</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
@@ -4949,16 +4949,16 @@
         </is>
       </c>
       <c r="E68" s="4" t="n">
-        <v>68524.09</v>
+        <v>68993.41</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>1358334.55</v>
+        <v>1339369.98</v>
       </c>
       <c r="G68" t="n">
         <v>31</v>
       </c>
       <c r="H68" s="6" t="n">
-        <v>12.2</v>
+        <v>12.3</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
@@ -4986,16 +4986,16 @@
         </is>
       </c>
       <c r="E69" s="4" t="n">
-        <v>61546.13</v>
+        <v>56209.44</v>
       </c>
       <c r="F69" s="4" t="n">
-        <v>1330805.61</v>
+        <v>1325302.22</v>
       </c>
       <c r="G69" t="n">
         <v>31</v>
       </c>
       <c r="H69" s="6" t="n">
-        <v>32.8</v>
+        <v>31.15</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
@@ -5023,16 +5023,16 @@
         </is>
       </c>
       <c r="E70" s="4" t="n">
-        <v>95259.66</v>
+        <v>86353.39</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>1216792.23</v>
+        <v>1186761.63</v>
       </c>
       <c r="G70" t="n">
         <v>31</v>
       </c>
       <c r="H70" s="6" t="n">
-        <v>70.42</v>
+        <v>68.12</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
@@ -5060,16 +5060,16 @@
         </is>
       </c>
       <c r="E71" s="4" t="n">
-        <v>42035.59</v>
+        <v>41799.04</v>
       </c>
       <c r="F71" s="4" t="n">
-        <v>1137291.52</v>
+        <v>1121574.47</v>
       </c>
       <c r="G71" t="n">
         <v>31</v>
       </c>
       <c r="H71" s="6" t="n">
-        <v>33.2</v>
+        <v>33.09</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
@@ -5097,16 +5097,16 @@
         </is>
       </c>
       <c r="E72" s="4" t="n">
-        <v>32891.97</v>
+        <v>33032.75</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>1117489.88</v>
+        <v>1118030.38</v>
       </c>
       <c r="G72" t="n">
         <v>31</v>
       </c>
       <c r="H72" s="6" t="n">
-        <v>5.88</v>
+        <v>5.94</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
@@ -5134,16 +5134,16 @@
         </is>
       </c>
       <c r="E73" s="4" t="n">
-        <v>40120.6</v>
+        <v>36536.83</v>
       </c>
       <c r="F73" s="4" t="n">
-        <v>1109651.39</v>
+        <v>1099805.67</v>
       </c>
       <c r="G73" t="n">
         <v>31</v>
       </c>
       <c r="H73" s="6" t="n">
-        <v>12.41</v>
+        <v>10.96</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
@@ -5154,7 +5154,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Nonso Amadi</t>
+          <t>Banky W.</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5163,7 +5163,7 @@
         </is>
       </c>
       <c r="C74" s="4" t="n">
-        <v>13207.45</v>
+        <v>35815.65</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5171,16 +5171,16 @@
         </is>
       </c>
       <c r="E74" s="4" t="n">
-        <v>37448.05</v>
+        <v>27387.56</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>1007699.69</v>
+        <v>997904.86</v>
       </c>
       <c r="G74" t="n">
         <v>31</v>
       </c>
       <c r="H74" s="6" t="n">
-        <v>15.46</v>
+        <v>-3.63</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
@@ -5191,7 +5191,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Banky W.</t>
+          <t>Lil Kesh</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5200,7 +5200,7 @@
         </is>
       </c>
       <c r="C75" s="4" t="n">
-        <v>35815.65</v>
+        <v>4792.05</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5208,16 +5208,16 @@
         </is>
       </c>
       <c r="E75" s="4" t="n">
-        <v>28480.24</v>
+        <v>83859.06</v>
       </c>
       <c r="F75" s="4" t="n">
-        <v>1006403.41</v>
+        <v>996519.41</v>
       </c>
       <c r="G75" t="n">
         <v>31</v>
       </c>
       <c r="H75" s="6" t="n">
-        <v>-3.11</v>
+        <v>48.41</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
@@ -5228,7 +5228,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Lil Kesh</t>
+          <t>Nonso Amadi</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5237,7 +5237,7 @@
         </is>
       </c>
       <c r="C76" s="4" t="n">
-        <v>4792.05</v>
+        <v>13207.45</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5245,16 +5245,16 @@
         </is>
       </c>
       <c r="E76" s="4" t="n">
-        <v>83473.95</v>
+        <v>36934.92</v>
       </c>
       <c r="F76" s="4" t="n">
-        <v>1005015.26</v>
+        <v>992763.14</v>
       </c>
       <c r="G76" t="n">
         <v>31</v>
       </c>
       <c r="H76" s="6" t="n">
-        <v>48.31</v>
+        <v>15.24</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
@@ -5282,10 +5282,10 @@
         </is>
       </c>
       <c r="E77" s="4" t="n">
-        <v>46325.16</v>
+        <v>47254.02</v>
       </c>
       <c r="F77" s="4" t="n">
-        <v>962515.16</v>
+        <v>947347.5</v>
       </c>
       <c r="G77" t="n">
         <v>30</v>
@@ -5317,16 +5317,16 @@
         </is>
       </c>
       <c r="E78" s="4" t="n">
-        <v>35865.73</v>
+        <v>37666.82</v>
       </c>
       <c r="F78" s="4" t="n">
-        <v>935501.5</v>
+        <v>930877.75</v>
       </c>
       <c r="G78" t="n">
         <v>31</v>
       </c>
       <c r="H78" s="6" t="n">
-        <v>11.66</v>
+        <v>12.42</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -5337,7 +5337,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Cruel Santino</t>
+          <t>D'banj</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5346,7 +5346,7 @@
         </is>
       </c>
       <c r="C79" s="4" t="n">
-        <v>0</v>
+        <v>16161.24</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5354,25 +5354,27 @@
         </is>
       </c>
       <c r="E79" s="4" t="n">
-        <v>46224.15</v>
+        <v>49967.22</v>
       </c>
       <c r="F79" s="4" t="n">
-        <v>909918.3199999999</v>
+        <v>901206.4399999999</v>
       </c>
       <c r="G79" t="n">
-        <v>30</v>
-      </c>
-      <c r="H79" t="inlineStr"/>
+        <v>31</v>
+      </c>
+      <c r="H79" s="6" t="n">
+        <v>16.85</v>
+      </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>UNK</t>
+          <t>OBS</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>D'banj</t>
+          <t>Cruel Santino</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5381,7 +5383,7 @@
         </is>
       </c>
       <c r="C80" s="4" t="n">
-        <v>16161.24</v>
+        <v>0</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5389,20 +5391,18 @@
         </is>
       </c>
       <c r="E80" s="4" t="n">
-        <v>50741.15</v>
+        <v>47459.84</v>
       </c>
       <c r="F80" s="4" t="n">
-        <v>906627.4399999999</v>
+        <v>893338.29</v>
       </c>
       <c r="G80" t="n">
-        <v>31</v>
-      </c>
-      <c r="H80" s="6" t="n">
-        <v>17.09</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr">
         <is>
-          <t>OBS</t>
+          <t>UNK</t>
         </is>
       </c>
     </row>
@@ -5426,16 +5426,16 @@
         </is>
       </c>
       <c r="E81" s="4" t="n">
-        <v>23369.17</v>
+        <v>24751</v>
       </c>
       <c r="F81" s="4" t="n">
-        <v>900571.7</v>
+        <v>886087.89</v>
       </c>
       <c r="G81" t="n">
         <v>31</v>
       </c>
       <c r="H81" s="6" t="n">
-        <v>3.51</v>
+        <v>4.33</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
@@ -5463,10 +5463,10 @@
         </is>
       </c>
       <c r="E82" s="4" t="n">
-        <v>87773.06</v>
+        <v>81234.35000000001</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v>871292.89</v>
+        <v>852027.35</v>
       </c>
       <c r="G82" t="n">
         <v>20</v>
@@ -5498,16 +5498,16 @@
         </is>
       </c>
       <c r="E83" s="4" t="n">
-        <v>65517.75</v>
+        <v>61443.32</v>
       </c>
       <c r="F83" s="4" t="n">
-        <v>798805.01</v>
+        <v>784060.16</v>
       </c>
       <c r="G83" t="n">
         <v>31</v>
       </c>
       <c r="H83" s="6" t="n">
-        <v>44.52</v>
+        <v>43.25</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
@@ -5535,13 +5535,13 @@
         </is>
       </c>
       <c r="E84" s="4" t="n">
-        <v>61182.36</v>
+        <v>54881.06</v>
       </c>
       <c r="F84" s="4" t="n">
-        <v>731170.11</v>
+        <v>725090.13</v>
       </c>
       <c r="G84" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr">
@@ -5570,10 +5570,10 @@
         </is>
       </c>
       <c r="E85" s="4" t="n">
-        <v>37041.25</v>
+        <v>32823.12</v>
       </c>
       <c r="F85" s="4" t="n">
-        <v>657071.9300000001</v>
+        <v>642819.1</v>
       </c>
       <c r="G85" t="n">
         <v>29</v>
@@ -5588,7 +5588,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Odunsi (The Engine)</t>
+          <t>Show Dem Camp</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5597,7 +5597,7 @@
         </is>
       </c>
       <c r="C86" s="4" t="n">
-        <v>10381.4</v>
+        <v>4079.36</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -5605,16 +5605,16 @@
         </is>
       </c>
       <c r="E86" s="4" t="n">
-        <v>17025.74</v>
+        <v>42181.79</v>
       </c>
       <c r="F86" s="4" t="n">
-        <v>604469.79</v>
+        <v>608210.34</v>
       </c>
       <c r="G86" t="n">
         <v>31</v>
       </c>
       <c r="H86" s="6" t="n">
-        <v>7.06</v>
+        <v>38.02</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
@@ -5625,7 +5625,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Show Dem Camp</t>
+          <t>Odunsi (The Engine)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5634,7 +5634,7 @@
         </is>
       </c>
       <c r="C87" s="4" t="n">
-        <v>4079.36</v>
+        <v>10381.4</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -5642,16 +5642,16 @@
         </is>
       </c>
       <c r="E87" s="4" t="n">
-        <v>43272</v>
+        <v>15294.91</v>
       </c>
       <c r="F87" s="4" t="n">
-        <v>600116.88</v>
+        <v>598270.86</v>
       </c>
       <c r="G87" t="n">
         <v>31</v>
       </c>
       <c r="H87" s="6" t="n">
-        <v>38.5</v>
+        <v>5.49</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
@@ -5679,16 +5679,16 @@
         </is>
       </c>
       <c r="E88" s="4" t="n">
-        <v>37735.06</v>
+        <v>35676.19</v>
       </c>
       <c r="F88" s="4" t="n">
-        <v>587945.99</v>
+        <v>563878.72</v>
       </c>
       <c r="G88" t="n">
         <v>31</v>
       </c>
       <c r="H88" s="6" t="n">
-        <v>35.31</v>
+        <v>34.26</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
@@ -5716,16 +5716,16 @@
         </is>
       </c>
       <c r="E89" s="4" t="n">
-        <v>52093.02</v>
+        <v>48686.35</v>
       </c>
       <c r="F89" s="4" t="n">
-        <v>582966.0699999999</v>
+        <v>559817.59</v>
       </c>
       <c r="G89" t="n">
         <v>31</v>
       </c>
       <c r="H89" s="6" t="n">
-        <v>81.53</v>
+        <v>79.84999999999999</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
@@ -5753,16 +5753,16 @@
         </is>
       </c>
       <c r="E90" s="4" t="n">
-        <v>33655.42</v>
+        <v>32421.13</v>
       </c>
       <c r="F90" s="4" t="n">
-        <v>535955.65</v>
+        <v>520162.83</v>
       </c>
       <c r="G90" t="n">
         <v>31</v>
       </c>
       <c r="H90" s="6" t="n">
-        <v>35.32</v>
+        <v>34.63</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
@@ -5773,7 +5773,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Mannywellz</t>
+          <t>Ajebutter22</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5782,7 +5782,7 @@
         </is>
       </c>
       <c r="C91" s="4" t="n">
-        <v>676.86</v>
+        <v>9381.68</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -5790,16 +5790,16 @@
         </is>
       </c>
       <c r="E91" s="4" t="n">
-        <v>43524.05</v>
+        <v>10269.37</v>
       </c>
       <c r="F91" s="4" t="n">
-        <v>502372.93</v>
+        <v>503473.88</v>
       </c>
       <c r="G91" t="n">
         <v>31</v>
       </c>
       <c r="H91" s="6" t="n">
-        <v>77.59</v>
+        <v>1.25</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
@@ -5810,7 +5810,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Ajebutter22</t>
+          <t>Mannywellz</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -5819,7 +5819,7 @@
         </is>
       </c>
       <c r="C92" s="4" t="n">
-        <v>9381.68</v>
+        <v>676.86</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -5827,16 +5827,16 @@
         </is>
       </c>
       <c r="E92" s="4" t="n">
-        <v>11533.35</v>
+        <v>42582.54</v>
       </c>
       <c r="F92" s="4" t="n">
-        <v>498638.04</v>
+        <v>494966.75</v>
       </c>
       <c r="G92" t="n">
         <v>31</v>
       </c>
       <c r="H92" s="6" t="n">
-        <v>2.89</v>
+        <v>77.05</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
@@ -5864,10 +5864,10 @@
         </is>
       </c>
       <c r="E93" s="4" t="n">
-        <v>18686.44</v>
+        <v>19657.01</v>
       </c>
       <c r="F93" s="4" t="n">
-        <v>466105.35</v>
+        <v>466690.96</v>
       </c>
       <c r="G93" t="n">
         <v>29</v>
@@ -5899,16 +5899,16 @@
         </is>
       </c>
       <c r="E94" s="4" t="n">
-        <v>18314</v>
+        <v>17085.66</v>
       </c>
       <c r="F94" s="4" t="n">
-        <v>425474.96</v>
+        <v>417084.98</v>
       </c>
       <c r="G94" t="n">
         <v>31</v>
       </c>
       <c r="H94" s="6" t="n">
-        <v>25.01</v>
+        <v>23.82</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
@@ -5919,7 +5919,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>9ice</t>
+          <t>Seyi Shay</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -5928,7 +5928,7 @@
         </is>
       </c>
       <c r="C95" s="4" t="n">
-        <v>4576.79</v>
+        <v>12339.17</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -5936,16 +5936,16 @@
         </is>
       </c>
       <c r="E95" s="4" t="n">
-        <v>31432.47</v>
+        <v>12442.66</v>
       </c>
       <c r="F95" s="4" t="n">
-        <v>420585.21</v>
+        <v>411683.33</v>
       </c>
       <c r="G95" t="n">
         <v>31</v>
       </c>
       <c r="H95" s="6" t="n">
-        <v>30.44</v>
+        <v>0.12</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
@@ -5956,7 +5956,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Seyi Shay</t>
+          <t>9ice</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -5965,7 +5965,7 @@
         </is>
       </c>
       <c r="C96" s="4" t="n">
-        <v>12339.17</v>
+        <v>4576.79</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -5973,16 +5973,16 @@
         </is>
       </c>
       <c r="E96" s="4" t="n">
-        <v>13120.63</v>
+        <v>27918.53</v>
       </c>
       <c r="F96" s="4" t="n">
-        <v>417153.75</v>
+        <v>406603.46</v>
       </c>
       <c r="G96" t="n">
         <v>31</v>
       </c>
       <c r="H96" s="6" t="n">
-        <v>0.85</v>
+        <v>28.33</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
@@ -6010,16 +6010,16 @@
         </is>
       </c>
       <c r="E97" s="4" t="n">
-        <v>40098.23</v>
+        <v>39408.8</v>
       </c>
       <c r="F97" s="4" t="n">
-        <v>414204.4</v>
+        <v>399028.45</v>
       </c>
       <c r="G97" t="n">
         <v>31</v>
       </c>
       <c r="H97" s="6" t="n">
-        <v>40.66</v>
+        <v>40.32</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
@@ -6047,16 +6047,16 @@
         </is>
       </c>
       <c r="E98" s="4" t="n">
-        <v>26516.5</v>
+        <v>27452.76</v>
       </c>
       <c r="F98" s="4" t="n">
-        <v>389248.18</v>
+        <v>385260.33</v>
       </c>
       <c r="G98" t="n">
         <v>31</v>
       </c>
       <c r="H98" s="6" t="n">
-        <v>24.75</v>
+        <v>25.35</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
@@ -6084,16 +6084,16 @@
         </is>
       </c>
       <c r="E99" s="4" t="n">
-        <v>18970.97</v>
+        <v>20541.76</v>
       </c>
       <c r="F99" s="4" t="n">
-        <v>371057.65</v>
+        <v>362610.32</v>
       </c>
       <c r="G99" t="n">
         <v>31</v>
       </c>
       <c r="H99" s="6" t="n">
-        <v>29.04</v>
+        <v>30.46</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
@@ -6121,10 +6121,10 @@
         </is>
       </c>
       <c r="E100" s="4" t="n">
-        <v>9277.639999999999</v>
+        <v>8526.059999999999</v>
       </c>
       <c r="F100" s="4" t="n">
-        <v>310665.23</v>
+        <v>302160.49</v>
       </c>
       <c r="G100" t="n">
         <v>30</v>
@@ -6156,16 +6156,16 @@
         </is>
       </c>
       <c r="E101" s="4" t="n">
-        <v>16960.91</v>
+        <v>16158.7</v>
       </c>
       <c r="F101" s="4" t="n">
-        <v>295198.4</v>
+        <v>285528.72</v>
       </c>
       <c r="G101" t="n">
         <v>31</v>
       </c>
       <c r="H101" s="6" t="n">
-        <v>20.36</v>
+        <v>19.56</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
@@ -6193,16 +6193,16 @@
         </is>
       </c>
       <c r="E102" s="4" t="n">
-        <v>34503.01</v>
+        <v>32532.98</v>
       </c>
       <c r="F102" s="4" t="n">
-        <v>294222.45</v>
+        <v>278764.79</v>
       </c>
       <c r="G102" t="n">
         <v>31</v>
       </c>
       <c r="H102" s="6" t="n">
-        <v>102.3</v>
+        <v>100.67</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
@@ -6230,16 +6230,16 @@
         </is>
       </c>
       <c r="E103" s="4" t="n">
-        <v>15522.25</v>
+        <v>15627.05</v>
       </c>
       <c r="F103" s="4" t="n">
-        <v>286862.95</v>
+        <v>273463.37</v>
       </c>
       <c r="G103" t="n">
         <v>31</v>
       </c>
       <c r="H103" s="6" t="n">
-        <v>31.45</v>
+        <v>31.57</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
@@ -6267,16 +6267,16 @@
         </is>
       </c>
       <c r="E104" s="4" t="n">
-        <v>9322.450000000001</v>
+        <v>9169.43</v>
       </c>
       <c r="F104" s="4" t="n">
-        <v>249395.6</v>
+        <v>247030.36</v>
       </c>
       <c r="G104" t="n">
         <v>31</v>
       </c>
       <c r="H104" s="6" t="n">
-        <v>1.99</v>
+        <v>1.76</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
@@ -6287,7 +6287,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Lady Donli</t>
+          <t>DJ Spinall</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6296,7 +6296,7 @@
         </is>
       </c>
       <c r="C105" s="4" t="n">
-        <v>1887.84</v>
+        <v>0</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -6304,27 +6304,25 @@
         </is>
       </c>
       <c r="E105" s="4" t="n">
-        <v>8841.59</v>
+        <v>0.11</v>
       </c>
       <c r="F105" s="4" t="n">
-        <v>240796.29</v>
+        <v>239503.03</v>
       </c>
       <c r="G105" t="n">
-        <v>31</v>
-      </c>
-      <c r="H105" s="6" t="n">
-        <v>23.73</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="H105" t="inlineStr"/>
       <c r="I105" t="inlineStr">
         <is>
-          <t>OBS</t>
+          <t>UNK</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>DJ Spinall</t>
+          <t>Lady Donli</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -6333,7 +6331,7 @@
         </is>
       </c>
       <c r="C106" s="4" t="n">
-        <v>0</v>
+        <v>1887.84</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -6341,18 +6339,20 @@
         </is>
       </c>
       <c r="E106" s="4" t="n">
-        <v>0.11</v>
+        <v>8764.059999999999</v>
       </c>
       <c r="F106" s="4" t="n">
-        <v>239500.8</v>
+        <v>237163.5</v>
       </c>
       <c r="G106" t="n">
-        <v>30</v>
-      </c>
-      <c r="H106" t="inlineStr"/>
+        <v>31</v>
+      </c>
+      <c r="H106" s="6" t="n">
+        <v>23.58</v>
+      </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>UNK</t>
+          <t>OBS</t>
         </is>
       </c>
     </row>
@@ -6376,16 +6376,16 @@
         </is>
       </c>
       <c r="E107" s="4" t="n">
-        <v>9687.07</v>
+        <v>9319.35</v>
       </c>
       <c r="F107" s="4" t="n">
-        <v>232600.68</v>
+        <v>230011.74</v>
       </c>
       <c r="G107" t="n">
         <v>31</v>
       </c>
       <c r="H107" s="6" t="n">
-        <v>19.08</v>
+        <v>18.45</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
@@ -6396,7 +6396,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Terry Apala</t>
+          <t>Dremo</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -6405,7 +6405,7 @@
         </is>
       </c>
       <c r="C108" s="4" t="n">
-        <v>899.4400000000001</v>
+        <v>2892.97</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -6413,16 +6413,16 @@
         </is>
       </c>
       <c r="E108" s="4" t="n">
-        <v>42004.59</v>
+        <v>18594.7</v>
       </c>
       <c r="F108" s="4" t="n">
-        <v>228901.74</v>
+        <v>213981.29</v>
       </c>
       <c r="G108" t="n">
         <v>31</v>
       </c>
       <c r="H108" s="6" t="n">
-        <v>69.92</v>
+        <v>29.26</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
@@ -6433,7 +6433,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Dremo</t>
+          <t>Terry Apala</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -6442,7 +6442,7 @@
         </is>
       </c>
       <c r="C109" s="4" t="n">
-        <v>2892.97</v>
+        <v>899.4400000000001</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -6450,16 +6450,16 @@
         </is>
       </c>
       <c r="E109" s="4" t="n">
-        <v>18870.39</v>
+        <v>37473.47</v>
       </c>
       <c r="F109" s="4" t="n">
-        <v>217986.17</v>
+        <v>205422.94</v>
       </c>
       <c r="G109" t="n">
         <v>31</v>
       </c>
       <c r="H109" s="6" t="n">
-        <v>29.52</v>
+        <v>67.27</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
@@ -6487,16 +6487,16 @@
         </is>
       </c>
       <c r="E110" s="4" t="n">
-        <v>9454.43</v>
+        <v>10842.17</v>
       </c>
       <c r="F110" s="4" t="n">
-        <v>183193.22</v>
+        <v>183525.51</v>
       </c>
       <c r="G110" t="n">
         <v>31</v>
       </c>
       <c r="H110" s="6" t="n">
-        <v>12.32</v>
+        <v>14.46</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
@@ -6524,16 +6524,16 @@
         </is>
       </c>
       <c r="E111" s="4" t="n">
-        <v>20181.94</v>
+        <v>19830.87</v>
       </c>
       <c r="F111" s="4" t="n">
-        <v>174555.1</v>
+        <v>173183.83</v>
       </c>
       <c r="G111" t="n">
         <v>31</v>
       </c>
       <c r="H111" s="6" t="n">
-        <v>40.51</v>
+        <v>40.17</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
@@ -6544,7 +6544,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Portable</t>
+          <t>Prettyboy D-O</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -6553,7 +6553,7 @@
         </is>
       </c>
       <c r="C112" s="4" t="n">
-        <v>0</v>
+        <v>741.95</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -6561,25 +6561,27 @@
         </is>
       </c>
       <c r="E112" s="4" t="n">
-        <v>0</v>
+        <v>5072.12</v>
       </c>
       <c r="F112" s="4" t="n">
-        <v>166960.31</v>
+        <v>165213.51</v>
       </c>
       <c r="G112" t="n">
-        <v>5</v>
-      </c>
-      <c r="H112" t="inlineStr"/>
+        <v>31</v>
+      </c>
+      <c r="H112" s="6" t="n">
+        <v>30.36</v>
+      </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>UNK</t>
+          <t>OBS</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Prettyboy D-O</t>
+          <t>Portable</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -6588,7 +6590,7 @@
         </is>
       </c>
       <c r="C113" s="4" t="n">
-        <v>741.95</v>
+        <v>0</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -6596,20 +6598,18 @@
         </is>
       </c>
       <c r="E113" s="4" t="n">
-        <v>4800.86</v>
+        <v>0</v>
       </c>
       <c r="F113" s="4" t="n">
-        <v>160713.67</v>
+        <v>164003.82</v>
       </c>
       <c r="G113" t="n">
-        <v>31</v>
-      </c>
-      <c r="H113" s="6" t="n">
-        <v>29.38</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="H113" t="inlineStr"/>
       <c r="I113" t="inlineStr">
         <is>
-          <t>OBS</t>
+          <t>UNK</t>
         </is>
       </c>
     </row>
@@ -6633,16 +6633,16 @@
         </is>
       </c>
       <c r="E114" s="4" t="n">
-        <v>12317.42</v>
+        <v>12602.39</v>
       </c>
       <c r="F114" s="4" t="n">
-        <v>152623</v>
+        <v>151898.57</v>
       </c>
       <c r="G114" t="n">
         <v>31</v>
       </c>
       <c r="H114" s="6" t="n">
-        <v>34.88</v>
+        <v>35.3</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
@@ -6670,16 +6670,16 @@
         </is>
       </c>
       <c r="E115" s="4" t="n">
-        <v>15860.7</v>
+        <v>13970.6</v>
       </c>
       <c r="F115" s="4" t="n">
-        <v>147783.54</v>
+        <v>137474.13</v>
       </c>
       <c r="G115" t="n">
         <v>31</v>
       </c>
       <c r="H115" s="6" t="n">
-        <v>71.92</v>
+        <v>68.94</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
@@ -6707,10 +6707,10 @@
         </is>
       </c>
       <c r="E116" s="4" t="n">
-        <v>7304.07</v>
+        <v>7034.79</v>
       </c>
       <c r="F116" s="4" t="n">
-        <v>125109.67</v>
+        <v>123484.25</v>
       </c>
       <c r="G116" t="n">
         <v>30</v>
@@ -6742,16 +6742,16 @@
         </is>
       </c>
       <c r="E117" s="4" t="n">
-        <v>2787.64</v>
+        <v>2916.07</v>
       </c>
       <c r="F117" s="4" t="n">
-        <v>116450.06</v>
+        <v>115047.37</v>
       </c>
       <c r="G117" t="n">
         <v>31</v>
       </c>
       <c r="H117" s="6" t="n">
-        <v>8.56</v>
+        <v>9.23</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
@@ -6779,16 +6779,16 @@
         </is>
       </c>
       <c r="E118" s="4" t="n">
-        <v>8854.809999999999</v>
+        <v>8265.73</v>
       </c>
       <c r="F118" s="4" t="n">
-        <v>113196.23</v>
+        <v>110289.07</v>
       </c>
       <c r="G118" t="n">
         <v>31</v>
       </c>
       <c r="H118" s="6" t="n">
-        <v>18.57</v>
+        <v>17.45</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
@@ -6816,16 +6816,16 @@
         </is>
       </c>
       <c r="E119" s="4" t="n">
-        <v>4680.29</v>
+        <v>4631.42</v>
       </c>
       <c r="F119" s="4" t="n">
-        <v>104709.28</v>
+        <v>103425.45</v>
       </c>
       <c r="G119" t="n">
         <v>31</v>
       </c>
       <c r="H119" s="6" t="n">
-        <v>10.14</v>
+        <v>9.98</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
@@ -6853,16 +6853,16 @@
         </is>
       </c>
       <c r="E120" s="4" t="n">
-        <v>8090.08</v>
+        <v>8714.08</v>
       </c>
       <c r="F120" s="4" t="n">
-        <v>94672.5</v>
+        <v>92056.2</v>
       </c>
       <c r="G120" t="n">
         <v>31</v>
       </c>
       <c r="H120" s="6" t="n">
-        <v>37.35</v>
+        <v>38.76</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
@@ -6890,16 +6890,16 @@
         </is>
       </c>
       <c r="E121" s="4" t="n">
-        <v>7252.59</v>
+        <v>7240</v>
       </c>
       <c r="F121" s="4" t="n">
-        <v>93322.39999999999</v>
+        <v>91471.78999999999</v>
       </c>
       <c r="G121" t="n">
         <v>31</v>
       </c>
       <c r="H121" s="6" t="n">
-        <v>34.57</v>
+        <v>34.54</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
@@ -6910,7 +6910,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Sound Sultan</t>
+          <t>Lagbaja</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -6919,7 +6919,7 @@
         </is>
       </c>
       <c r="C122" s="4" t="n">
-        <v>1656.35</v>
+        <v>508.99</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -6927,16 +6927,16 @@
         </is>
       </c>
       <c r="E122" s="4" t="n">
-        <v>5772.79</v>
+        <v>2733.93</v>
       </c>
       <c r="F122" s="4" t="n">
-        <v>84223.42999999999</v>
+        <v>90294.23</v>
       </c>
       <c r="G122" t="n">
         <v>31</v>
       </c>
       <c r="H122" s="6" t="n">
-        <v>18.79</v>
+        <v>26.1</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
@@ -6947,7 +6947,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Lagbaja</t>
+          <t>Sound Sultan</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -6956,7 +6956,7 @@
         </is>
       </c>
       <c r="C123" s="4" t="n">
-        <v>508.99</v>
+        <v>1656.35</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -6964,16 +6964,16 @@
         </is>
       </c>
       <c r="E123" s="4" t="n">
-        <v>2621.68</v>
+        <v>5622.49</v>
       </c>
       <c r="F123" s="4" t="n">
-        <v>84058.69</v>
+        <v>83321.61</v>
       </c>
       <c r="G123" t="n">
         <v>31</v>
       </c>
       <c r="H123" s="6" t="n">
-        <v>25.37</v>
+        <v>18.36</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -7001,16 +7001,16 @@
         </is>
       </c>
       <c r="E124" s="4" t="n">
-        <v>4847.59</v>
+        <v>4948.08</v>
       </c>
       <c r="F124" s="4" t="n">
-        <v>78149.47</v>
+        <v>78268.5</v>
       </c>
       <c r="G124" t="n">
         <v>31</v>
       </c>
       <c r="H124" s="6" t="n">
-        <v>44.81</v>
+        <v>45.22</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
@@ -7038,16 +7038,16 @@
         </is>
       </c>
       <c r="E125" s="4" t="n">
-        <v>5502.47</v>
+        <v>4870.04</v>
       </c>
       <c r="F125" s="4" t="n">
-        <v>53988.76</v>
+        <v>51265.01</v>
       </c>
       <c r="G125" t="n">
         <v>31</v>
       </c>
       <c r="H125" s="6" t="n">
-        <v>46.62</v>
+        <v>44.17</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
@@ -7075,16 +7075,16 @@
         </is>
       </c>
       <c r="E126" s="4" t="n">
-        <v>2439.6</v>
+        <v>2263.15</v>
       </c>
       <c r="F126" s="4" t="n">
-        <v>43741.67</v>
+        <v>43359.32</v>
       </c>
       <c r="G126" t="n">
         <v>31</v>
       </c>
       <c r="H126" s="6" t="n">
-        <v>-4.81</v>
+        <v>-5.79</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
@@ -7112,10 +7112,10 @@
         </is>
       </c>
       <c r="E127" s="4" t="n">
-        <v>707.27</v>
+        <v>652.1900000000001</v>
       </c>
       <c r="F127" s="4" t="n">
-        <v>7522.13</v>
+        <v>7400.37</v>
       </c>
       <c r="G127" t="n">
         <v>30</v>
@@ -7147,16 +7147,16 @@
         </is>
       </c>
       <c r="E128" s="4" t="n">
-        <v>122.95</v>
+        <v>122.69</v>
       </c>
       <c r="F128" s="4" t="n">
-        <v>3355.25</v>
+        <v>3338.72</v>
       </c>
       <c r="G128" t="n">
         <v>31</v>
       </c>
       <c r="H128" s="6" t="n">
-        <v>7.39</v>
+        <v>7.36</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         <v>26.11</v>
       </c>
       <c r="F129" s="4" t="n">
-        <v>883.5700000000001</v>
+        <v>884.51</v>
       </c>
       <c r="G129" t="n">
         <v>31</v>
@@ -7224,7 +7224,7 @@
         <v>0</v>
       </c>
       <c r="F130" s="4" t="n">
-        <v>12.06</v>
+        <v>20.08</v>
       </c>
       <c r="G130" t="n">
         <v>4</v>
